--- a/XRD_Results/CuS B1_CuS_XRD_Analysis.xlsx
+++ b/XRD_Results/CuS B1_CuS_XRD_Analysis.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,19 +500,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>32.202</v>
+        <v>30.606</v>
       </c>
       <c r="C4" t="n">
-        <v>2.77754</v>
+        <v>2.91866</v>
       </c>
       <c r="D4" t="n">
-        <v>1366.38</v>
+        <v>736.524</v>
       </c>
       <c r="E4" t="n">
-        <v>738.8189720279742</v>
+        <v>30.27249417249436</v>
       </c>
       <c r="F4" t="n">
-        <v>70.3489180297484</v>
+        <v>37.92039293823271</v>
       </c>
     </row>
     <row r="5">
@@ -520,19 +520,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>48.183</v>
+        <v>32.202</v>
       </c>
       <c r="C5" t="n">
-        <v>1.88708</v>
+        <v>2.77754</v>
       </c>
       <c r="D5" t="n">
-        <v>1942.29</v>
+        <v>1366.38</v>
       </c>
       <c r="E5" t="n">
-        <v>1312.670331002334</v>
+        <v>738.8189720279742</v>
       </c>
       <c r="F5" t="n">
-        <v>100</v>
+        <v>70.3489180297484</v>
       </c>
     </row>
     <row r="6">
@@ -540,19 +540,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>52.849</v>
+        <v>35.394</v>
       </c>
       <c r="C6" t="n">
-        <v>1.73095</v>
+        <v>2.53401</v>
       </c>
       <c r="D6" t="n">
-        <v>1000</v>
+        <v>655.7619999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>269.3306200466208</v>
+        <v>35.3962331002333</v>
       </c>
       <c r="F6" t="n">
-        <v>51.4856174927534</v>
+        <v>33.76231149828295</v>
       </c>
     </row>
     <row r="7">
@@ -560,19 +560,719 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
+        <v>36.315</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.47184</v>
+      </c>
+      <c r="D7" t="n">
+        <v>655.524</v>
+      </c>
+      <c r="E7" t="n">
+        <v>35.70010256410251</v>
+      </c>
+      <c r="F7" t="n">
+        <v>33.75005792131968</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>37.932</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2.37013</v>
+      </c>
+      <c r="D8" t="n">
+        <v>671.571</v>
+      </c>
+      <c r="E8" t="n">
+        <v>37.57773193473213</v>
+      </c>
+      <c r="F8" t="n">
+        <v>34.5762476252259</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>39.016</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.30671</v>
+      </c>
+      <c r="D9" t="n">
+        <v>704.095</v>
+      </c>
+      <c r="E9" t="n">
+        <v>81.61939393939406</v>
+      </c>
+      <c r="F9" t="n">
+        <v>36.25076584856021</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>40.121</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.24569</v>
+      </c>
+      <c r="D10" t="n">
+        <v>663.2859999999999</v>
+      </c>
+      <c r="E10" t="n">
+        <v>32.60576923076928</v>
+      </c>
+      <c r="F10" t="n">
+        <v>34.14968928429843</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>40.735</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.21325</v>
+      </c>
+      <c r="D11" t="n">
+        <v>664.524</v>
+      </c>
+      <c r="E11" t="n">
+        <v>37.67823076923094</v>
+      </c>
+      <c r="F11" t="n">
+        <v>34.21342847875446</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>41.267</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2.18594</v>
+      </c>
+      <c r="D12" t="n">
+        <v>676.905</v>
+      </c>
+      <c r="E12" t="n">
+        <v>39.03099067599089</v>
+      </c>
+      <c r="F12" t="n">
+        <v>34.85087190893224</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>41.881</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2.15531</v>
+      </c>
+      <c r="D13" t="n">
+        <v>675.333</v>
+      </c>
+      <c r="E13" t="n">
+        <v>36.55203030303051</v>
+      </c>
+      <c r="F13" t="n">
+        <v>34.76993651823363</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>43.006</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2.10148</v>
+      </c>
+      <c r="D14" t="n">
+        <v>711.476</v>
+      </c>
+      <c r="E14" t="n">
+        <v>40.65626573426584</v>
+      </c>
+      <c r="F14" t="n">
+        <v>36.63078119127422</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>43.866</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2.06228</v>
+      </c>
+      <c r="D15" t="n">
+        <v>708.8099999999999</v>
+      </c>
+      <c r="E15" t="n">
+        <v>49.50725641025645</v>
+      </c>
+      <c r="F15" t="n">
+        <v>36.49352053503853</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>45.973</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.97251</v>
+      </c>
+      <c r="D16" t="n">
+        <v>709.143</v>
+      </c>
+      <c r="E16" t="n">
+        <v>33.30796736596744</v>
+      </c>
+      <c r="F16" t="n">
+        <v>36.51066524566362</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="n">
+        <v>46.853</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.9375</v>
+      </c>
+      <c r="D17" t="n">
+        <v>770.7619999999999</v>
+      </c>
+      <c r="E17" t="n">
+        <v>34.60022843822844</v>
+      </c>
+      <c r="F17" t="n">
+        <v>39.6831575099496</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>48.183</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1.88708</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1942.29</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1312.670331002334</v>
+      </c>
+      <c r="F18" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>50.598</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.80254</v>
+      </c>
+      <c r="D19" t="n">
+        <v>773.095</v>
+      </c>
+      <c r="E19" t="n">
+        <v>39.30611188811201</v>
+      </c>
+      <c r="F19" t="n">
+        <v>39.80327345556019</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>52.849</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.73095</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E20" t="n">
+        <v>269.3306200466208</v>
+      </c>
+      <c r="F20" t="n">
+        <v>51.4856174927534</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>54.629</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.67867</v>
+      </c>
+      <c r="D21" t="n">
+        <v>752.2859999999999</v>
+      </c>
+      <c r="E21" t="n">
+        <v>29.98480419580437</v>
+      </c>
+      <c r="F21" t="n">
+        <v>38.73190924115348</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="n">
+        <v>55.877</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.6441</v>
+      </c>
+      <c r="D22" t="n">
+        <v>749.095</v>
+      </c>
+      <c r="E22" t="n">
+        <v>38.98323310023318</v>
+      </c>
+      <c r="F22" t="n">
+        <v>38.56761863573411</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57.351</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.60531</v>
+      </c>
+      <c r="D23" t="n">
+        <v>827.2859999999999</v>
+      </c>
+      <c r="E23" t="n">
+        <v>44.05834032634039</v>
+      </c>
+      <c r="F23" t="n">
+        <v>42.59333055310999</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="n">
         <v>59.335</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C24" t="n">
         <v>1.55626</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D24" t="n">
         <v>1160.67</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E24" t="n">
         <v>458.3228881118894</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F24" t="n">
         <v>59.7578116553141</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="n">
+        <v>61.648</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.50332</v>
+      </c>
+      <c r="D25" t="n">
+        <v>760.2380000000001</v>
+      </c>
+      <c r="E25" t="n">
+        <v>39.67465734265761</v>
+      </c>
+      <c r="F25" t="n">
+        <v>39.14132287145586</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="n">
+        <v>62.302</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.48908</v>
+      </c>
+      <c r="D26" t="n">
+        <v>740.667</v>
+      </c>
+      <c r="E26" t="n">
+        <v>49.22194172494176</v>
+      </c>
+      <c r="F26" t="n">
+        <v>38.13369785150518</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="n">
+        <v>63.101</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1.47216</v>
+      </c>
+      <c r="D27" t="n">
+        <v>756.2859999999999</v>
+      </c>
+      <c r="E27" t="n">
+        <v>68.22245687645704</v>
+      </c>
+      <c r="F27" t="n">
+        <v>38.93785171112449</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>65.536</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1.42323</v>
+      </c>
+      <c r="D28" t="n">
+        <v>711.524</v>
+      </c>
+      <c r="E28" t="n">
+        <v>42.85821445221461</v>
+      </c>
+      <c r="F28" t="n">
+        <v>36.63325250091387</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="n">
+        <v>66.19</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1.41072</v>
+      </c>
+      <c r="D29" t="n">
+        <v>718.857</v>
+      </c>
+      <c r="E29" t="n">
+        <v>29.93228205128219</v>
+      </c>
+      <c r="F29" t="n">
+        <v>37.01079653398823</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="n">
+        <v>67.541</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1.38576</v>
+      </c>
+      <c r="D30" t="n">
+        <v>735.1900000000001</v>
+      </c>
+      <c r="E30" t="n">
+        <v>54.91938694638702</v>
+      </c>
+      <c r="F30" t="n">
+        <v>37.85171112449737</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="n">
+        <v>67.95</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1.37841</v>
+      </c>
+      <c r="D31" t="n">
+        <v>721.905</v>
+      </c>
+      <c r="E31" t="n">
+        <v>47.02834965034981</v>
+      </c>
+      <c r="F31" t="n">
+        <v>37.16772469610614</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="n">
+        <v>68.72799999999999</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1.3647</v>
+      </c>
+      <c r="D32" t="n">
+        <v>708.524</v>
+      </c>
+      <c r="E32" t="n">
+        <v>30.52301398601412</v>
+      </c>
+      <c r="F32" t="n">
+        <v>36.47879564843561</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="n">
+        <v>70.16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1.3403</v>
+      </c>
+      <c r="D33" t="n">
+        <v>743.2859999999999</v>
+      </c>
+      <c r="E33" t="n">
+        <v>64.25235431235456</v>
+      </c>
+      <c r="F33" t="n">
+        <v>38.2685386837187</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="n">
+        <v>71.797</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1.31372</v>
+      </c>
+      <c r="D34" t="n">
+        <v>693.571</v>
+      </c>
+      <c r="E34" t="n">
+        <v>38.92793006993008</v>
+      </c>
+      <c r="F34" t="n">
+        <v>35.70893121006647</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="n">
+        <v>73.782</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1.2832</v>
+      </c>
+      <c r="D35" t="n">
+        <v>729.333</v>
+      </c>
+      <c r="E35" t="n">
+        <v>51.68265734265742</v>
+      </c>
+      <c r="F35" t="n">
+        <v>37.55015986284231</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="n">
+        <v>74.294</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1.27563</v>
+      </c>
+      <c r="D36" t="n">
+        <v>724.2380000000001</v>
+      </c>
+      <c r="E36" t="n">
+        <v>30.23593240093248</v>
+      </c>
+      <c r="F36" t="n">
+        <v>37.28784064171674</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="n">
+        <v>74.539</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1.27203</v>
+      </c>
+      <c r="D37" t="n">
+        <v>731.2859999999999</v>
+      </c>
+      <c r="E37" t="n">
+        <v>82.93523310023329</v>
+      </c>
+      <c r="F37" t="n">
+        <v>37.65071127380566</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="n">
+        <v>75.971</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1.25157</v>
+      </c>
+      <c r="D38" t="n">
+        <v>668.667</v>
+      </c>
+      <c r="E38" t="n">
+        <v>31.29283216783222</v>
+      </c>
+      <c r="F38" t="n">
+        <v>34.42673339202694</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="n">
+        <v>76.46299999999999</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1.24475</v>
+      </c>
+      <c r="D39" t="n">
+        <v>684.476</v>
+      </c>
+      <c r="E39" t="n">
+        <v>33.68230769230775</v>
+      </c>
+      <c r="F39" t="n">
+        <v>35.24066951896987</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="n">
+        <v>76.995</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1.23747</v>
+      </c>
+      <c r="D40" t="n">
+        <v>677.048</v>
+      </c>
+      <c r="E40" t="n">
+        <v>31.7052890442892</v>
+      </c>
+      <c r="F40" t="n">
+        <v>34.8582343522337</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="n">
+        <v>78.161</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1.2219</v>
+      </c>
+      <c r="D41" t="n">
+        <v>704.476</v>
+      </c>
+      <c r="E41" t="n">
+        <v>50.68701631701822</v>
+      </c>
+      <c r="F41" t="n">
+        <v>36.27038186882495</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79.36799999999999</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1.20632</v>
+      </c>
+      <c r="D42" t="n">
+        <v>703.619</v>
+      </c>
+      <c r="E42" t="n">
+        <v>41.84309557109566</v>
+      </c>
+      <c r="F42" t="n">
+        <v>36.22625869463366</v>
       </c>
     </row>
   </sheetData>
@@ -20686,7 +21386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21496,35 +22196,35 @@
         <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>32.202</v>
+        <v>30.606</v>
       </c>
       <c r="C13" t="n">
-        <v>2.77754</v>
+        <v>2.91866</v>
       </c>
       <c r="D13" t="n">
-        <v>1366.38</v>
+        <v>736.524</v>
       </c>
       <c r="E13" t="n">
-        <v>70.3489180297484</v>
+        <v>37.92039293823271</v>
       </c>
       <c r="F13" t="n">
-        <v>32.2076</v>
+        <v>30.5264</v>
       </c>
       <c r="G13" t="n">
-        <v>2.777</v>
+        <v>2.926</v>
       </c>
       <c r="H13" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="J13" t="n">
-        <v>0.00560000000000116</v>
+        <v>0.07960000000000278</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>6 0 8</t>
+          <t>3 1 12</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -21561,35 +22261,35 @@
         <v>3</v>
       </c>
       <c r="B14" t="n">
-        <v>32.202</v>
+        <v>30.606</v>
       </c>
       <c r="C14" t="n">
-        <v>2.77754</v>
+        <v>2.91866</v>
       </c>
       <c r="D14" t="n">
-        <v>1366.38</v>
+        <v>736.524</v>
       </c>
       <c r="E14" t="n">
-        <v>70.3489180297484</v>
+        <v>37.92039293823271</v>
       </c>
       <c r="F14" t="n">
-        <v>32.0508</v>
+        <v>30.7772</v>
       </c>
       <c r="G14" t="n">
-        <v>2.7902</v>
+        <v>2.9027</v>
       </c>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I14" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1511999999999958</v>
+        <v>0.1711999999999989</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2 5 2</t>
+          <t>-3 5 1</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -21626,35 +22326,35 @@
         <v>3</v>
       </c>
       <c r="B15" t="n">
-        <v>32.202</v>
+        <v>30.606</v>
       </c>
       <c r="C15" t="n">
-        <v>2.77754</v>
+        <v>2.91866</v>
       </c>
       <c r="D15" t="n">
-        <v>1366.38</v>
+        <v>736.524</v>
       </c>
       <c r="E15" t="n">
-        <v>70.3489180297484</v>
+        <v>37.92039293823271</v>
       </c>
       <c r="F15" t="n">
-        <v>32.0508</v>
+        <v>30.7772</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7902</v>
+        <v>2.9027</v>
       </c>
       <c r="H15" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I15" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1511999999999958</v>
+        <v>0.1711999999999989</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4 5 1</t>
+          <t>3 5 1</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -21691,55 +22391,55 @@
         <v>3</v>
       </c>
       <c r="B16" t="n">
-        <v>32.202</v>
+        <v>30.606</v>
       </c>
       <c r="C16" t="n">
-        <v>2.77754</v>
+        <v>2.91866</v>
       </c>
       <c r="D16" t="n">
-        <v>1366.38</v>
+        <v>736.524</v>
       </c>
       <c r="E16" t="n">
-        <v>70.3489180297484</v>
+        <v>37.92039293823271</v>
       </c>
       <c r="F16" t="n">
-        <v>31.982</v>
+        <v>30.3755</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7961</v>
+        <v>2.9402</v>
       </c>
       <c r="H16" t="n">
-        <v>999</v>
+        <v>8</v>
       </c>
       <c r="I16" t="n">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2199999999999989</v>
+        <v>0.2305000000000028</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1 0 3</t>
+          <t>-3 2 4</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Covellite</t>
+          <t>Djurleite</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>000752233</t>
+          <t>000711383</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -21753,62 +22453,62 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B17" t="n">
-        <v>48.183</v>
+        <v>30.606</v>
       </c>
       <c r="C17" t="n">
-        <v>1.88708</v>
+        <v>2.91866</v>
       </c>
       <c r="D17" t="n">
-        <v>1942.29</v>
+        <v>736.524</v>
       </c>
       <c r="E17" t="n">
-        <v>100</v>
+        <v>37.92039293823271</v>
       </c>
       <c r="F17" t="n">
-        <v>48.2657</v>
+        <v>30.3755</v>
       </c>
       <c r="G17" t="n">
-        <v>1.884</v>
+        <v>2.9402</v>
       </c>
       <c r="H17" t="n">
-        <v>618</v>
+        <v>8</v>
       </c>
       <c r="I17" t="n">
-        <v>61.86186186186187</v>
+        <v>8</v>
       </c>
       <c r="J17" t="n">
-        <v>0.08270000000000266</v>
+        <v>0.2305000000000028</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1 1 0</t>
+          <t>3 2 4</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Covellite</t>
+          <t>Djurleite</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>000752233</t>
+          <t>000711383</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -21818,62 +22518,62 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B18" t="n">
-        <v>48.183</v>
+        <v>30.606</v>
       </c>
       <c r="C18" t="n">
-        <v>1.88708</v>
+        <v>2.91866</v>
       </c>
       <c r="D18" t="n">
-        <v>1942.29</v>
+        <v>736.524</v>
       </c>
       <c r="E18" t="n">
-        <v>100</v>
+        <v>37.92039293823271</v>
       </c>
       <c r="F18" t="n">
-        <v>48.0177</v>
+        <v>30.8969</v>
       </c>
       <c r="G18" t="n">
-        <v>1.8931</v>
+        <v>2.8918</v>
       </c>
       <c r="H18" t="n">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="I18" t="n">
-        <v>16.51651651651652</v>
+        <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>0.165300000000002</v>
+        <v>0.290899999999997</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1 0 7</t>
+          <t>-5 3 3</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Covellite</t>
+          <t>Djurleite</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>000752233</t>
+          <t>000711383</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -21883,62 +22583,62 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B19" t="n">
-        <v>52.849</v>
+        <v>30.606</v>
       </c>
       <c r="C19" t="n">
-        <v>1.73095</v>
+        <v>2.91866</v>
       </c>
       <c r="D19" t="n">
-        <v>1000</v>
+        <v>736.524</v>
       </c>
       <c r="E19" t="n">
-        <v>51.4856174927534</v>
+        <v>37.92039293823271</v>
       </c>
       <c r="F19" t="n">
-        <v>53.0112</v>
+        <v>30.8969</v>
       </c>
       <c r="G19" t="n">
-        <v>1.726</v>
+        <v>2.8918</v>
       </c>
       <c r="H19" t="n">
-        <v>256</v>
+        <v>21</v>
       </c>
       <c r="I19" t="n">
-        <v>25.62562562562562</v>
+        <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1622000000000057</v>
+        <v>0.290899999999997</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1 0 8</t>
+          <t>6 4 1</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Covellite</t>
+          <t>Djurleite</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>000752233</t>
+          <t>000711383</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -21948,38 +22648,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B20" t="n">
-        <v>52.849</v>
+        <v>32.202</v>
       </c>
       <c r="C20" t="n">
-        <v>1.73095</v>
+        <v>2.77754</v>
       </c>
       <c r="D20" t="n">
-        <v>1000</v>
+        <v>1366.38</v>
       </c>
       <c r="E20" t="n">
-        <v>51.4856174927534</v>
+        <v>70.3489180297484</v>
       </c>
       <c r="F20" t="n">
-        <v>52.6163</v>
+        <v>32.2076</v>
       </c>
       <c r="G20" t="n">
-        <v>1.738</v>
+        <v>2.777</v>
       </c>
       <c r="H20" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="I20" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2326999999999941</v>
+        <v>0.00560000000000116</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>6 6 10</t>
+          <t>6 0 8</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -22003,7 +22703,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -22013,64 +22713,3631 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" t="n">
+        <v>32.202</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2.77754</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1366.38</v>
+      </c>
+      <c r="E21" t="n">
+        <v>70.3489180297484</v>
+      </c>
+      <c r="F21" t="n">
+        <v>32.0508</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.7902</v>
+      </c>
+      <c r="H21" t="n">
         <v>6</v>
       </c>
-      <c r="B21" t="n">
+      <c r="I21" t="n">
+        <v>6</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.1511999999999958</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2 5 2</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" t="n">
+        <v>32.202</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2.77754</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1366.38</v>
+      </c>
+      <c r="E22" t="n">
+        <v>70.3489180297484</v>
+      </c>
+      <c r="F22" t="n">
+        <v>32.0508</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.7902</v>
+      </c>
+      <c r="H22" t="n">
+        <v>6</v>
+      </c>
+      <c r="I22" t="n">
+        <v>6</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.1511999999999958</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>4 5 1</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" t="n">
+        <v>32.202</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2.77754</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1366.38</v>
+      </c>
+      <c r="E23" t="n">
+        <v>70.3489180297484</v>
+      </c>
+      <c r="F23" t="n">
+        <v>31.982</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.7961</v>
+      </c>
+      <c r="H23" t="n">
+        <v>999</v>
+      </c>
+      <c r="I23" t="n">
+        <v>100</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.2199999999999989</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>1 0 3</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Covellite</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" t="n">
+        <v>35.394</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2.53401</v>
+      </c>
+      <c r="D24" t="n">
+        <v>655.7619999999999</v>
+      </c>
+      <c r="E24" t="n">
+        <v>33.76231149828295</v>
+      </c>
+      <c r="F24" t="n">
+        <v>35.4426</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.5306</v>
+      </c>
+      <c r="H24" t="n">
+        <v>10</v>
+      </c>
+      <c r="I24" t="n">
+        <v>10</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.04860000000000042</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>-2 6 1</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" t="n">
+        <v>35.394</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2.53401</v>
+      </c>
+      <c r="D25" t="n">
+        <v>655.7619999999999</v>
+      </c>
+      <c r="E25" t="n">
+        <v>33.76231149828295</v>
+      </c>
+      <c r="F25" t="n">
+        <v>35.4426</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.5306</v>
+      </c>
+      <c r="H25" t="n">
+        <v>10</v>
+      </c>
+      <c r="I25" t="n">
+        <v>10</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.04860000000000042</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2 6 1</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" t="n">
+        <v>35.394</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2.53401</v>
+      </c>
+      <c r="D26" t="n">
+        <v>655.7619999999999</v>
+      </c>
+      <c r="E26" t="n">
+        <v>33.76231149828295</v>
+      </c>
+      <c r="F26" t="n">
+        <v>35.3317</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.5383</v>
+      </c>
+      <c r="H26" t="n">
+        <v>7</v>
+      </c>
+      <c r="I26" t="n">
+        <v>7.000000000000001</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.06230000000000047</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>-2 5 3</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" t="n">
+        <v>35.394</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2.53401</v>
+      </c>
+      <c r="D27" t="n">
+        <v>655.7619999999999</v>
+      </c>
+      <c r="E27" t="n">
+        <v>33.76231149828295</v>
+      </c>
+      <c r="F27" t="n">
+        <v>35.3317</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.5383</v>
+      </c>
+      <c r="H27" t="n">
+        <v>7</v>
+      </c>
+      <c r="I27" t="n">
+        <v>7.000000000000001</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.06230000000000047</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2 5 3</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" t="n">
+        <v>35.394</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2.53401</v>
+      </c>
+      <c r="D28" t="n">
+        <v>655.7619999999999</v>
+      </c>
+      <c r="E28" t="n">
+        <v>33.76231149828295</v>
+      </c>
+      <c r="F28" t="n">
+        <v>35.5434</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.5236</v>
+      </c>
+      <c r="H28" t="n">
+        <v>16</v>
+      </c>
+      <c r="I28" t="n">
+        <v>16</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.1494</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>-5 5 2</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>5</v>
+      </c>
+      <c r="B29" t="n">
+        <v>35.394</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2.53401</v>
+      </c>
+      <c r="D29" t="n">
+        <v>655.7619999999999</v>
+      </c>
+      <c r="E29" t="n">
+        <v>33.76231149828295</v>
+      </c>
+      <c r="F29" t="n">
+        <v>35.5434</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2.5236</v>
+      </c>
+      <c r="H29" t="n">
+        <v>16</v>
+      </c>
+      <c r="I29" t="n">
+        <v>16</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.1494</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>5 5 2</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>5</v>
+      </c>
+      <c r="B30" t="n">
+        <v>35.394</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2.53401</v>
+      </c>
+      <c r="D30" t="n">
+        <v>655.7619999999999</v>
+      </c>
+      <c r="E30" t="n">
+        <v>33.76231149828295</v>
+      </c>
+      <c r="F30" t="n">
+        <v>35.0955</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.5548</v>
+      </c>
+      <c r="H30" t="n">
+        <v>14</v>
+      </c>
+      <c r="I30" t="n">
+        <v>14</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.2984999999999971</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>7 3 3</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>5</v>
+      </c>
+      <c r="B31" t="n">
+        <v>35.394</v>
+      </c>
+      <c r="C31" t="n">
+        <v>2.53401</v>
+      </c>
+      <c r="D31" t="n">
+        <v>655.7619999999999</v>
+      </c>
+      <c r="E31" t="n">
+        <v>33.76231149828295</v>
+      </c>
+      <c r="F31" t="n">
+        <v>35.0955</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.5548</v>
+      </c>
+      <c r="H31" t="n">
+        <v>14</v>
+      </c>
+      <c r="I31" t="n">
+        <v>14</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.2984999999999971</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>-8 2 3</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B32" t="n">
+        <v>36.315</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2.47184</v>
+      </c>
+      <c r="D32" t="n">
+        <v>655.524</v>
+      </c>
+      <c r="E32" t="n">
+        <v>33.75005792131968</v>
+      </c>
+      <c r="F32" t="n">
+        <v>36.2877</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.4736</v>
+      </c>
+      <c r="H32" t="n">
+        <v>15</v>
+      </c>
+      <c r="I32" t="n">
+        <v>15</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.02729999999999677</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>3 6 1</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>6</v>
+      </c>
+      <c r="B33" t="n">
+        <v>36.315</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2.47184</v>
+      </c>
+      <c r="D33" t="n">
+        <v>655.524</v>
+      </c>
+      <c r="E33" t="n">
+        <v>33.75005792131968</v>
+      </c>
+      <c r="F33" t="n">
+        <v>36.2877</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2.4736</v>
+      </c>
+      <c r="H33" t="n">
+        <v>15</v>
+      </c>
+      <c r="I33" t="n">
+        <v>15</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.02729999999999677</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>6 4 3</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>6</v>
+      </c>
+      <c r="B34" t="n">
+        <v>36.315</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2.47184</v>
+      </c>
+      <c r="D34" t="n">
+        <v>655.524</v>
+      </c>
+      <c r="E34" t="n">
+        <v>33.75005792131968</v>
+      </c>
+      <c r="F34" t="n">
+        <v>36.3813</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2.4674</v>
+      </c>
+      <c r="H34" t="n">
+        <v>14</v>
+      </c>
+      <c r="I34" t="n">
+        <v>14</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.06630000000000535</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>10 1 2</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>6</v>
+      </c>
+      <c r="B35" t="n">
+        <v>36.315</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2.47184</v>
+      </c>
+      <c r="D35" t="n">
+        <v>655.524</v>
+      </c>
+      <c r="E35" t="n">
+        <v>33.75005792131968</v>
+      </c>
+      <c r="F35" t="n">
+        <v>36.3813</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2.4674</v>
+      </c>
+      <c r="H35" t="n">
+        <v>14</v>
+      </c>
+      <c r="I35" t="n">
+        <v>14</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.06630000000000535</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>-3 2 5</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>6</v>
+      </c>
+      <c r="B36" t="n">
+        <v>36.315</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2.47184</v>
+      </c>
+      <c r="D36" t="n">
+        <v>655.524</v>
+      </c>
+      <c r="E36" t="n">
+        <v>33.75005792131968</v>
+      </c>
+      <c r="F36" t="n">
+        <v>36.426</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.4645</v>
+      </c>
+      <c r="H36" t="n">
+        <v>999</v>
+      </c>
+      <c r="I36" t="n">
+        <v>100</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.1110000000000042</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2 0 0</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>CuCl</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>CuCl</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>000822117</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>6</v>
+      </c>
+      <c r="B37" t="n">
+        <v>36.315</v>
+      </c>
+      <c r="C37" t="n">
+        <v>2.47184</v>
+      </c>
+      <c r="D37" t="n">
+        <v>655.524</v>
+      </c>
+      <c r="E37" t="n">
+        <v>33.75005792131968</v>
+      </c>
+      <c r="F37" t="n">
+        <v>36.1452</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2.483</v>
+      </c>
+      <c r="H37" t="n">
+        <v>5</v>
+      </c>
+      <c r="I37" t="n">
+        <v>5</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.1697999999999951</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>6 0 11</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>6</v>
+      </c>
+      <c r="B38" t="n">
+        <v>36.315</v>
+      </c>
+      <c r="C38" t="n">
+        <v>2.47184</v>
+      </c>
+      <c r="D38" t="n">
+        <v>655.524</v>
+      </c>
+      <c r="E38" t="n">
+        <v>33.75005792131968</v>
+      </c>
+      <c r="F38" t="n">
+        <v>36.1321</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.4839</v>
+      </c>
+      <c r="H38" t="n">
+        <v>12</v>
+      </c>
+      <c r="I38" t="n">
+        <v>12</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.1828999999999965</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>-3 5 3</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>6</v>
+      </c>
+      <c r="B39" t="n">
+        <v>36.315</v>
+      </c>
+      <c r="C39" t="n">
+        <v>2.47184</v>
+      </c>
+      <c r="D39" t="n">
+        <v>655.524</v>
+      </c>
+      <c r="E39" t="n">
+        <v>33.75005792131968</v>
+      </c>
+      <c r="F39" t="n">
+        <v>36.1321</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2.4839</v>
+      </c>
+      <c r="H39" t="n">
+        <v>12</v>
+      </c>
+      <c r="I39" t="n">
+        <v>12</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.1828999999999965</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>3 5 3</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>7</v>
+      </c>
+      <c r="B40" t="n">
+        <v>37.932</v>
+      </c>
+      <c r="C40" t="n">
+        <v>2.37013</v>
+      </c>
+      <c r="D40" t="n">
+        <v>671.571</v>
+      </c>
+      <c r="E40" t="n">
+        <v>34.5762476252259</v>
+      </c>
+      <c r="F40" t="n">
+        <v>38.0912</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2.3605</v>
+      </c>
+      <c r="H40" t="n">
+        <v>6</v>
+      </c>
+      <c r="I40" t="n">
+        <v>6</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.1591999999999985</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>3 6 2</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>7</v>
+      </c>
+      <c r="B41" t="n">
+        <v>37.932</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2.37013</v>
+      </c>
+      <c r="D41" t="n">
+        <v>671.571</v>
+      </c>
+      <c r="E41" t="n">
+        <v>34.5762476252259</v>
+      </c>
+      <c r="F41" t="n">
+        <v>38.0912</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2.3605</v>
+      </c>
+      <c r="H41" t="n">
+        <v>6</v>
+      </c>
+      <c r="I41" t="n">
+        <v>6</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.1591999999999985</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>3 1</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>7</v>
+      </c>
+      <c r="B42" t="n">
+        <v>37.932</v>
+      </c>
+      <c r="C42" t="n">
+        <v>2.37013</v>
+      </c>
+      <c r="D42" t="n">
+        <v>671.571</v>
+      </c>
+      <c r="E42" t="n">
+        <v>34.5762476252259</v>
+      </c>
+      <c r="F42" t="n">
+        <v>37.7724</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2.3797</v>
+      </c>
+      <c r="H42" t="n">
+        <v>39</v>
+      </c>
+      <c r="I42" t="n">
+        <v>39</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.1596000000000046</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1 1</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>7</v>
+      </c>
+      <c r="B43" t="n">
+        <v>37.932</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2.37013</v>
+      </c>
+      <c r="D43" t="n">
+        <v>671.571</v>
+      </c>
+      <c r="E43" t="n">
+        <v>34.5762476252259</v>
+      </c>
+      <c r="F43" t="n">
+        <v>37.7724</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2.3797</v>
+      </c>
+      <c r="H43" t="n">
+        <v>39</v>
+      </c>
+      <c r="I43" t="n">
+        <v>39</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.1596000000000046</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>11 1 1</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>7</v>
+      </c>
+      <c r="B44" t="n">
+        <v>37.932</v>
+      </c>
+      <c r="C44" t="n">
+        <v>2.37013</v>
+      </c>
+      <c r="D44" t="n">
+        <v>671.571</v>
+      </c>
+      <c r="E44" t="n">
+        <v>34.5762476252259</v>
+      </c>
+      <c r="F44" t="n">
+        <v>37.6867</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2.3849</v>
+      </c>
+      <c r="H44" t="n">
+        <v>76</v>
+      </c>
+      <c r="I44" t="n">
+        <v>76</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.2453000000000003</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>8 0 4</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>7</v>
+      </c>
+      <c r="B45" t="n">
+        <v>37.932</v>
+      </c>
+      <c r="C45" t="n">
+        <v>2.37013</v>
+      </c>
+      <c r="D45" t="n">
+        <v>671.571</v>
+      </c>
+      <c r="E45" t="n">
+        <v>34.5762476252259</v>
+      </c>
+      <c r="F45" t="n">
+        <v>37.6867</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2.3849</v>
+      </c>
+      <c r="H45" t="n">
+        <v>76</v>
+      </c>
+      <c r="I45" t="n">
+        <v>76</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.2453000000000003</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2 2</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>7</v>
+      </c>
+      <c r="B46" t="n">
+        <v>37.932</v>
+      </c>
+      <c r="C46" t="n">
+        <v>2.37013</v>
+      </c>
+      <c r="D46" t="n">
+        <v>671.571</v>
+      </c>
+      <c r="E46" t="n">
+        <v>34.5762476252259</v>
+      </c>
+      <c r="F46" t="n">
+        <v>37.6687</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2.386</v>
+      </c>
+      <c r="H46" t="n">
+        <v>20</v>
+      </c>
+      <c r="I46" t="n">
+        <v>20</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.263300000000001</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>6 0 12</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>8</v>
+      </c>
+      <c r="B47" t="n">
+        <v>39.016</v>
+      </c>
+      <c r="C47" t="n">
+        <v>2.30671</v>
+      </c>
+      <c r="D47" t="n">
+        <v>704.095</v>
+      </c>
+      <c r="E47" t="n">
+        <v>36.25076584856021</v>
+      </c>
+      <c r="F47" t="n">
+        <v>39.0597</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2.3042</v>
+      </c>
+      <c r="H47" t="n">
+        <v>126</v>
+      </c>
+      <c r="I47" t="n">
+        <v>12.61261261261261</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.04370000000000118</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>1 0 5</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Covellite</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>8</v>
+      </c>
+      <c r="B48" t="n">
+        <v>39.016</v>
+      </c>
+      <c r="C48" t="n">
+        <v>2.30671</v>
+      </c>
+      <c r="D48" t="n">
+        <v>704.095</v>
+      </c>
+      <c r="E48" t="n">
+        <v>36.25076584856021</v>
+      </c>
+      <c r="F48" t="n">
+        <v>39.1604</v>
+      </c>
+      <c r="G48" t="n">
+        <v>2.2985</v>
+      </c>
+      <c r="H48" t="n">
+        <v>6</v>
+      </c>
+      <c r="I48" t="n">
+        <v>6</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.1444000000000045</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>-4 6 2</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>8</v>
+      </c>
+      <c r="B49" t="n">
+        <v>39.016</v>
+      </c>
+      <c r="C49" t="n">
+        <v>2.30671</v>
+      </c>
+      <c r="D49" t="n">
+        <v>704.095</v>
+      </c>
+      <c r="E49" t="n">
+        <v>36.25076584856021</v>
+      </c>
+      <c r="F49" t="n">
+        <v>39.1604</v>
+      </c>
+      <c r="G49" t="n">
+        <v>2.2985</v>
+      </c>
+      <c r="H49" t="n">
+        <v>6</v>
+      </c>
+      <c r="I49" t="n">
+        <v>6</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.1444000000000045</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>-6 1 5</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>8</v>
+      </c>
+      <c r="B50" t="n">
+        <v>39.016</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2.30671</v>
+      </c>
+      <c r="D50" t="n">
+        <v>704.095</v>
+      </c>
+      <c r="E50" t="n">
+        <v>36.25076584856021</v>
+      </c>
+      <c r="F50" t="n">
+        <v>39.1866</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2.297</v>
+      </c>
+      <c r="H50" t="n">
+        <v>25</v>
+      </c>
+      <c r="I50" t="n">
+        <v>25</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.1706000000000003</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>6 0 13</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>8</v>
+      </c>
+      <c r="B51" t="n">
+        <v>39.016</v>
+      </c>
+      <c r="C51" t="n">
+        <v>2.30671</v>
+      </c>
+      <c r="D51" t="n">
+        <v>704.095</v>
+      </c>
+      <c r="E51" t="n">
+        <v>36.25076584856021</v>
+      </c>
+      <c r="F51" t="n">
+        <v>38.8318</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2.3172</v>
+      </c>
+      <c r="H51" t="n">
+        <v>6</v>
+      </c>
+      <c r="I51" t="n">
+        <v>6</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.184199999999997</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>-5 2 5</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>8</v>
+      </c>
+      <c r="B52" t="n">
+        <v>39.016</v>
+      </c>
+      <c r="C52" t="n">
+        <v>2.30671</v>
+      </c>
+      <c r="D52" t="n">
+        <v>704.095</v>
+      </c>
+      <c r="E52" t="n">
+        <v>36.25076584856021</v>
+      </c>
+      <c r="F52" t="n">
+        <v>38.8318</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2.3172</v>
+      </c>
+      <c r="H52" t="n">
+        <v>6</v>
+      </c>
+      <c r="I52" t="n">
+        <v>6</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.184199999999997</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>5 4 4</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>8</v>
+      </c>
+      <c r="B53" t="n">
+        <v>39.016</v>
+      </c>
+      <c r="C53" t="n">
+        <v>2.30671</v>
+      </c>
+      <c r="D53" t="n">
+        <v>704.095</v>
+      </c>
+      <c r="E53" t="n">
+        <v>36.25076584856021</v>
+      </c>
+      <c r="F53" t="n">
+        <v>39.2897</v>
+      </c>
+      <c r="G53" t="n">
+        <v>2.2912</v>
+      </c>
+      <c r="H53" t="n">
+        <v>9</v>
+      </c>
+      <c r="I53" t="n">
+        <v>9</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.2737000000000052</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>7 5 2</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>8</v>
+      </c>
+      <c r="B54" t="n">
+        <v>39.016</v>
+      </c>
+      <c r="C54" t="n">
+        <v>2.30671</v>
+      </c>
+      <c r="D54" t="n">
+        <v>704.095</v>
+      </c>
+      <c r="E54" t="n">
+        <v>36.25076584856021</v>
+      </c>
+      <c r="F54" t="n">
+        <v>39.2897</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2.2912</v>
+      </c>
+      <c r="H54" t="n">
+        <v>9</v>
+      </c>
+      <c r="I54" t="n">
+        <v>9</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.2737000000000052</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>-7 5 2</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>8</v>
+      </c>
+      <c r="B55" t="n">
+        <v>39.016</v>
+      </c>
+      <c r="C55" t="n">
+        <v>2.30671</v>
+      </c>
+      <c r="D55" t="n">
+        <v>704.095</v>
+      </c>
+      <c r="E55" t="n">
+        <v>36.25076584856021</v>
+      </c>
+      <c r="F55" t="n">
+        <v>38.7261</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2.3233</v>
+      </c>
+      <c r="H55" t="n">
+        <v>8</v>
+      </c>
+      <c r="I55" t="n">
+        <v>8</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.2898999999999958</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>-5 6 1</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>8</v>
+      </c>
+      <c r="B56" t="n">
+        <v>39.016</v>
+      </c>
+      <c r="C56" t="n">
+        <v>2.30671</v>
+      </c>
+      <c r="D56" t="n">
+        <v>704.095</v>
+      </c>
+      <c r="E56" t="n">
+        <v>36.25076584856021</v>
+      </c>
+      <c r="F56" t="n">
+        <v>38.7261</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2.3233</v>
+      </c>
+      <c r="H56" t="n">
+        <v>8</v>
+      </c>
+      <c r="I56" t="n">
+        <v>8</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.2898999999999958</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>5 6 1</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>11</v>
+      </c>
+      <c r="B57" t="n">
+        <v>41.267</v>
+      </c>
+      <c r="C57" t="n">
+        <v>2.18594</v>
+      </c>
+      <c r="D57" t="n">
+        <v>676.905</v>
+      </c>
+      <c r="E57" t="n">
+        <v>34.85087190893224</v>
+      </c>
+      <c r="F57" t="n">
+        <v>41.2844</v>
+      </c>
+      <c r="G57" t="n">
+        <v>2.185</v>
+      </c>
+      <c r="H57" t="n">
+        <v>8</v>
+      </c>
+      <c r="I57" t="n">
+        <v>8</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.01739999999999498</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0 0 19</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>14</v>
+      </c>
+      <c r="B58" t="n">
+        <v>43.866</v>
+      </c>
+      <c r="C58" t="n">
+        <v>2.06228</v>
+      </c>
+      <c r="D58" t="n">
+        <v>708.8099999999999</v>
+      </c>
+      <c r="E58" t="n">
+        <v>36.49352053503853</v>
+      </c>
+      <c r="F58" t="n">
+        <v>43.9154</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H58" t="n">
+        <v>8</v>
+      </c>
+      <c r="I58" t="n">
+        <v>8</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.04939999999999856</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>1 0 20</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>15</v>
+      </c>
+      <c r="B59" t="n">
+        <v>45.973</v>
+      </c>
+      <c r="C59" t="n">
+        <v>1.97251</v>
+      </c>
+      <c r="D59" t="n">
+        <v>709.143</v>
+      </c>
+      <c r="E59" t="n">
+        <v>36.51066524566362</v>
+      </c>
+      <c r="F59" t="n">
+        <v>46.158</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1.965</v>
+      </c>
+      <c r="H59" t="n">
+        <v>12</v>
+      </c>
+      <c r="I59" t="n">
+        <v>12</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.1850000000000023</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>6 0 17</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>17</v>
+      </c>
+      <c r="B60" t="n">
+        <v>48.183</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1.88708</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1942.29</v>
+      </c>
+      <c r="E60" t="n">
+        <v>100</v>
+      </c>
+      <c r="F60" t="n">
+        <v>48.2657</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1.884</v>
+      </c>
+      <c r="H60" t="n">
+        <v>618</v>
+      </c>
+      <c r="I60" t="n">
+        <v>61.86186186186187</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.08270000000000266</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>1 1 0</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Covellite</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>17</v>
+      </c>
+      <c r="B61" t="n">
+        <v>48.183</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1.88708</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1942.29</v>
+      </c>
+      <c r="E61" t="n">
+        <v>100</v>
+      </c>
+      <c r="F61" t="n">
+        <v>48.0177</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1.8931</v>
+      </c>
+      <c r="H61" t="n">
+        <v>165</v>
+      </c>
+      <c r="I61" t="n">
+        <v>16.51651651651652</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.165300000000002</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>1 0 7</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Covellite</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>19</v>
+      </c>
+      <c r="B62" t="n">
+        <v>52.849</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1.73095</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E62" t="n">
+        <v>51.4856174927534</v>
+      </c>
+      <c r="F62" t="n">
+        <v>53.0112</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1.726</v>
+      </c>
+      <c r="H62" t="n">
+        <v>256</v>
+      </c>
+      <c r="I62" t="n">
+        <v>25.62562562562562</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.1622000000000057</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>1 0 8</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Covellite</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>19</v>
+      </c>
+      <c r="B63" t="n">
+        <v>52.849</v>
+      </c>
+      <c r="C63" t="n">
+        <v>1.73095</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E63" t="n">
+        <v>51.4856174927534</v>
+      </c>
+      <c r="F63" t="n">
+        <v>52.6163</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1.738</v>
+      </c>
+      <c r="H63" t="n">
+        <v>12</v>
+      </c>
+      <c r="I63" t="n">
+        <v>12</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.2326999999999941</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>6 6 10</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>20</v>
+      </c>
+      <c r="B64" t="n">
+        <v>54.629</v>
+      </c>
+      <c r="C64" t="n">
+        <v>1.67867</v>
+      </c>
+      <c r="D64" t="n">
+        <v>752.2859999999999</v>
+      </c>
+      <c r="E64" t="n">
+        <v>38.73190924115348</v>
+      </c>
+      <c r="F64" t="n">
+        <v>54.4403</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1.684</v>
+      </c>
+      <c r="H64" t="n">
+        <v>8</v>
+      </c>
+      <c r="I64" t="n">
+        <v>8</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.1886999999999972</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>4 2 22</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>23</v>
+      </c>
+      <c r="B65" t="n">
         <v>59.335</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C65" t="n">
         <v>1.55626</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D65" t="n">
         <v>1160.67</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E65" t="n">
         <v>59.7578116553141</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F65" t="n">
         <v>59.0765</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G65" t="n">
         <v>1.5624</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H65" t="n">
         <v>104</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I65" t="n">
         <v>10.41041041041041</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J65" t="n">
         <v>0.258499999999998</v>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>2 0 3</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>CuS</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>Covellite</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>CuS</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>000752233</t>
         </is>
       </c>
-      <c r="P21" t="n">
+      <c r="P65" t="n">
         <v>1</v>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>26</v>
+      </c>
+      <c r="B66" t="n">
+        <v>63.101</v>
+      </c>
+      <c r="C66" t="n">
+        <v>1.47216</v>
+      </c>
+      <c r="D66" t="n">
+        <v>756.2859999999999</v>
+      </c>
+      <c r="E66" t="n">
+        <v>38.93785171112449</v>
+      </c>
+      <c r="F66" t="n">
+        <v>63.0584</v>
+      </c>
+      <c r="G66" t="n">
+        <v>1.473</v>
+      </c>
+      <c r="H66" t="n">
+        <v>15</v>
+      </c>
+      <c r="I66" t="n">
+        <v>15</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.04260000000000019</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>12 0 13</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>27</v>
+      </c>
+      <c r="B67" t="n">
+        <v>65.536</v>
+      </c>
+      <c r="C67" t="n">
+        <v>1.42323</v>
+      </c>
+      <c r="D67" t="n">
+        <v>711.524</v>
+      </c>
+      <c r="E67" t="n">
+        <v>36.63325250091387</v>
+      </c>
+      <c r="F67" t="n">
+        <v>65.5515</v>
+      </c>
+      <c r="G67" t="n">
+        <v>1.4229</v>
+      </c>
+      <c r="H67" t="n">
+        <v>139</v>
+      </c>
+      <c r="I67" t="n">
+        <v>13.91391391391391</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.01550000000000296</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>2 2 2</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>CuCl</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>CuCl</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>000822117</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>27</v>
+      </c>
+      <c r="B68" t="n">
+        <v>65.536</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1.42323</v>
+      </c>
+      <c r="D68" t="n">
+        <v>711.524</v>
+      </c>
+      <c r="E68" t="n">
+        <v>36.63325250091387</v>
+      </c>
+      <c r="F68" t="n">
+        <v>65.4935</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1.424</v>
+      </c>
+      <c r="H68" t="n">
+        <v>8</v>
+      </c>
+      <c r="I68" t="n">
+        <v>8</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.04250000000000398</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>12 0 15</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>28</v>
+      </c>
+      <c r="B69" t="n">
+        <v>66.19</v>
+      </c>
+      <c r="C69" t="n">
+        <v>1.41072</v>
+      </c>
+      <c r="D69" t="n">
+        <v>718.857</v>
+      </c>
+      <c r="E69" t="n">
+        <v>37.01079653398823</v>
+      </c>
+      <c r="F69" t="n">
+        <v>66.4396</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1.406</v>
+      </c>
+      <c r="H69" t="n">
+        <v>8</v>
+      </c>
+      <c r="I69" t="n">
+        <v>8</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.2496000000000009</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>6 6 20</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>29</v>
+      </c>
+      <c r="B70" t="n">
+        <v>67.541</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1.38576</v>
+      </c>
+      <c r="D70" t="n">
+        <v>735.1900000000001</v>
+      </c>
+      <c r="E70" t="n">
+        <v>37.85171112449737</v>
+      </c>
+      <c r="F70" t="n">
+        <v>67.5258</v>
+      </c>
+      <c r="G70" t="n">
+        <v>1.386</v>
+      </c>
+      <c r="H70" t="n">
+        <v>8</v>
+      </c>
+      <c r="I70" t="n">
+        <v>8</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.015199999999993</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>0 0 30</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>31</v>
+      </c>
+      <c r="B71" t="n">
+        <v>68.72799999999999</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1.3647</v>
+      </c>
+      <c r="D71" t="n">
+        <v>708.524</v>
+      </c>
+      <c r="E71" t="n">
+        <v>36.47879564843561</v>
+      </c>
+      <c r="F71" t="n">
+        <v>68.9388</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1.361</v>
+      </c>
+      <c r="H71" t="n">
+        <v>8</v>
+      </c>
+      <c r="I71" t="n">
+        <v>8</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.2108000000000061</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>2 0 7</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>35</v>
+      </c>
+      <c r="B72" t="n">
+        <v>74.294</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1.27563</v>
+      </c>
+      <c r="D72" t="n">
+        <v>724.2380000000001</v>
+      </c>
+      <c r="E72" t="n">
+        <v>37.28784064171674</v>
+      </c>
+      <c r="F72" t="n">
+        <v>74.4939</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1.2727</v>
+      </c>
+      <c r="H72" t="n">
+        <v>57</v>
+      </c>
+      <c r="I72" t="n">
+        <v>5.705705705705705</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.1998999999999995</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>2 0 8</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Covellite</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>36</v>
+      </c>
+      <c r="B73" t="n">
+        <v>74.539</v>
+      </c>
+      <c r="C73" t="n">
+        <v>1.27203</v>
+      </c>
+      <c r="D73" t="n">
+        <v>731.2859999999999</v>
+      </c>
+      <c r="E73" t="n">
+        <v>37.65071127380566</v>
+      </c>
+      <c r="F73" t="n">
+        <v>74.4939</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1.2727</v>
+      </c>
+      <c r="H73" t="n">
+        <v>57</v>
+      </c>
+      <c r="I73" t="n">
+        <v>5.705705705705705</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.04510000000000502</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>2 0 8</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Covellite</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>38</v>
+      </c>
+      <c r="B74" t="n">
+        <v>76.46299999999999</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1.24475</v>
+      </c>
+      <c r="D74" t="n">
+        <v>684.476</v>
+      </c>
+      <c r="E74" t="n">
+        <v>35.24066951896987</v>
+      </c>
+      <c r="F74" t="n">
+        <v>76.73350000000001</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="H74" t="n">
+        <v>12</v>
+      </c>
+      <c r="I74" t="n">
+        <v>12</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.2705000000000126</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>6 0 31</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>39</v>
+      </c>
+      <c r="B75" t="n">
+        <v>76.995</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1.23747</v>
+      </c>
+      <c r="D75" t="n">
+        <v>677.048</v>
+      </c>
+      <c r="E75" t="n">
+        <v>34.8582343522337</v>
+      </c>
+      <c r="F75" t="n">
+        <v>76.73350000000001</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="H75" t="n">
+        <v>12</v>
+      </c>
+      <c r="I75" t="n">
+        <v>12</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.2614999999999981</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>6 0 31</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>41</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79.36799999999999</v>
+      </c>
+      <c r="C76" t="n">
+        <v>1.20632</v>
+      </c>
+      <c r="D76" t="n">
+        <v>703.619</v>
+      </c>
+      <c r="E76" t="n">
+        <v>36.22625869463366</v>
+      </c>
+      <c r="F76" t="n">
+        <v>79.6553</v>
+      </c>
+      <c r="G76" t="n">
+        <v>1.2027</v>
+      </c>
+      <c r="H76" t="n">
+        <v>53</v>
+      </c>
+      <c r="I76" t="n">
+        <v>5.305305305305305</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.2873000000000019</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>2 1 3</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Covellite</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q76" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
@@ -22087,7 +26354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22312,35 +26579,35 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>32.202</v>
+        <v>30.606</v>
       </c>
       <c r="C4" t="n">
-        <v>2.77754</v>
+        <v>2.91866</v>
       </c>
       <c r="D4" t="n">
-        <v>1366.38</v>
+        <v>736.524</v>
       </c>
       <c r="E4" t="n">
-        <v>70.3489180297484</v>
+        <v>37.92039293823271</v>
       </c>
       <c r="F4" t="n">
-        <v>32.2076</v>
+        <v>30.5264</v>
       </c>
       <c r="G4" t="n">
-        <v>2.777</v>
+        <v>2.926</v>
       </c>
       <c r="H4" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00560000000000116</v>
+        <v>0.07960000000000278</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>6 0 8</t>
+          <t>3 1 12</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -22377,55 +26644,55 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>48.183</v>
+        <v>32.202</v>
       </c>
       <c r="C5" t="n">
-        <v>1.88708</v>
+        <v>2.77754</v>
       </c>
       <c r="D5" t="n">
-        <v>1942.29</v>
+        <v>1366.38</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>70.3489180297484</v>
       </c>
       <c r="F5" t="n">
-        <v>48.2657</v>
+        <v>32.2076</v>
       </c>
       <c r="G5" t="n">
-        <v>1.884</v>
+        <v>2.777</v>
       </c>
       <c r="H5" t="n">
-        <v>618</v>
+        <v>30</v>
       </c>
       <c r="I5" t="n">
-        <v>61.86186186186187</v>
+        <v>30</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08270000000000266</v>
+        <v>0.00560000000000116</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1 1 0</t>
+          <t>6 0 8</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu39S28</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Covellite</t>
+          <t>Spionkopite</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu39S28</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>000752233</t>
+          <t>000360380</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -22442,55 +26709,55 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>52.849</v>
+        <v>35.394</v>
       </c>
       <c r="C6" t="n">
-        <v>1.73095</v>
+        <v>2.53401</v>
       </c>
       <c r="D6" t="n">
-        <v>1000</v>
+        <v>655.7619999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>51.4856174927534</v>
+        <v>33.76231149828295</v>
       </c>
       <c r="F6" t="n">
-        <v>53.0112</v>
+        <v>35.4426</v>
       </c>
       <c r="G6" t="n">
-        <v>1.726</v>
+        <v>2.5306</v>
       </c>
       <c r="H6" t="n">
-        <v>256</v>
+        <v>10</v>
       </c>
       <c r="I6" t="n">
-        <v>25.62562562562562</v>
+        <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1622000000000057</v>
+        <v>0.04860000000000042</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1 0 8</t>
+          <t>-2 6 1</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Covellite</t>
+          <t>Djurleite</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>000752233</t>
+          <t>000711383</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -22507,61 +26774,1292 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>59.335</v>
+        <v>36.315</v>
       </c>
       <c r="C7" t="n">
-        <v>1.55626</v>
+        <v>2.47184</v>
       </c>
       <c r="D7" t="n">
-        <v>1160.67</v>
+        <v>655.524</v>
       </c>
       <c r="E7" t="n">
-        <v>59.7578116553141</v>
+        <v>33.75005792131968</v>
       </c>
       <c r="F7" t="n">
-        <v>59.0765</v>
+        <v>36.2877</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5624</v>
+        <v>2.4736</v>
       </c>
       <c r="H7" t="n">
-        <v>104</v>
+        <v>15</v>
       </c>
       <c r="I7" t="n">
-        <v>10.41041041041041</v>
+        <v>15</v>
       </c>
       <c r="J7" t="n">
-        <v>0.258499999999998</v>
+        <v>0.02729999999999677</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2 0 3</t>
+          <t>3 6 1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Covellite</t>
+          <t>Djurleite</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>000752233</t>
+          <t>000711383</t>
         </is>
       </c>
       <c r="P7" t="n">
         <v>1</v>
       </c>
       <c r="Q7" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>37.932</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2.37013</v>
+      </c>
+      <c r="D8" t="n">
+        <v>671.571</v>
+      </c>
+      <c r="E8" t="n">
+        <v>34.5762476252259</v>
+      </c>
+      <c r="F8" t="n">
+        <v>38.0912</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.3605</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.1591999999999985</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>3 6 2</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>39.016</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.30671</v>
+      </c>
+      <c r="D9" t="n">
+        <v>704.095</v>
+      </c>
+      <c r="E9" t="n">
+        <v>36.25076584856021</v>
+      </c>
+      <c r="F9" t="n">
+        <v>39.0597</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.3042</v>
+      </c>
+      <c r="H9" t="n">
+        <v>126</v>
+      </c>
+      <c r="I9" t="n">
+        <v>12.61261261261261</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.04370000000000118</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>1 0 5</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Covellite</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>11</v>
+      </c>
+      <c r="B10" t="n">
+        <v>41.267</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.18594</v>
+      </c>
+      <c r="D10" t="n">
+        <v>676.905</v>
+      </c>
+      <c r="E10" t="n">
+        <v>34.85087190893224</v>
+      </c>
+      <c r="F10" t="n">
+        <v>41.2844</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.185</v>
+      </c>
+      <c r="H10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I10" t="n">
+        <v>8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01739999999999498</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0 0 19</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14</v>
+      </c>
+      <c r="B11" t="n">
+        <v>43.866</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.06228</v>
+      </c>
+      <c r="D11" t="n">
+        <v>708.8099999999999</v>
+      </c>
+      <c r="E11" t="n">
+        <v>36.49352053503853</v>
+      </c>
+      <c r="F11" t="n">
+        <v>43.9154</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H11" t="n">
+        <v>8</v>
+      </c>
+      <c r="I11" t="n">
+        <v>8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.04939999999999856</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1 0 20</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15</v>
+      </c>
+      <c r="B12" t="n">
+        <v>45.973</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.97251</v>
+      </c>
+      <c r="D12" t="n">
+        <v>709.143</v>
+      </c>
+      <c r="E12" t="n">
+        <v>36.51066524566362</v>
+      </c>
+      <c r="F12" t="n">
+        <v>46.158</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.965</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.1850000000000023</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>6 0 17</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17</v>
+      </c>
+      <c r="B13" t="n">
+        <v>48.183</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.88708</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1942.29</v>
+      </c>
+      <c r="E13" t="n">
+        <v>100</v>
+      </c>
+      <c r="F13" t="n">
+        <v>48.2657</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.884</v>
+      </c>
+      <c r="H13" t="n">
+        <v>618</v>
+      </c>
+      <c r="I13" t="n">
+        <v>61.86186186186187</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.08270000000000266</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>1 1 0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Covellite</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>19</v>
+      </c>
+      <c r="B14" t="n">
+        <v>52.849</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.73095</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E14" t="n">
+        <v>51.4856174927534</v>
+      </c>
+      <c r="F14" t="n">
+        <v>53.0112</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.726</v>
+      </c>
+      <c r="H14" t="n">
+        <v>256</v>
+      </c>
+      <c r="I14" t="n">
+        <v>25.62562562562562</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.1622000000000057</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1 0 8</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Covellite</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>54.629</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.67867</v>
+      </c>
+      <c r="D15" t="n">
+        <v>752.2859999999999</v>
+      </c>
+      <c r="E15" t="n">
+        <v>38.73190924115348</v>
+      </c>
+      <c r="F15" t="n">
+        <v>54.4403</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.684</v>
+      </c>
+      <c r="H15" t="n">
+        <v>8</v>
+      </c>
+      <c r="I15" t="n">
+        <v>8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.1886999999999972</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>4 2 22</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>23</v>
+      </c>
+      <c r="B16" t="n">
+        <v>59.335</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.55626</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1160.67</v>
+      </c>
+      <c r="E16" t="n">
+        <v>59.7578116553141</v>
+      </c>
+      <c r="F16" t="n">
+        <v>59.0765</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.5624</v>
+      </c>
+      <c r="H16" t="n">
+        <v>104</v>
+      </c>
+      <c r="I16" t="n">
+        <v>10.41041041041041</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.258499999999998</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2 0 3</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Covellite</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>26</v>
+      </c>
+      <c r="B17" t="n">
+        <v>63.101</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.47216</v>
+      </c>
+      <c r="D17" t="n">
+        <v>756.2859999999999</v>
+      </c>
+      <c r="E17" t="n">
+        <v>38.93785171112449</v>
+      </c>
+      <c r="F17" t="n">
+        <v>63.0584</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.473</v>
+      </c>
+      <c r="H17" t="n">
+        <v>15</v>
+      </c>
+      <c r="I17" t="n">
+        <v>15</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.04260000000000019</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>12 0 13</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>27</v>
+      </c>
+      <c r="B18" t="n">
+        <v>65.536</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1.42323</v>
+      </c>
+      <c r="D18" t="n">
+        <v>711.524</v>
+      </c>
+      <c r="E18" t="n">
+        <v>36.63325250091387</v>
+      </c>
+      <c r="F18" t="n">
+        <v>65.5515</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.4229</v>
+      </c>
+      <c r="H18" t="n">
+        <v>139</v>
+      </c>
+      <c r="I18" t="n">
+        <v>13.91391391391391</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.01550000000000296</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2 2 2</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>CuCl</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>CuCl</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>000822117</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>28</v>
+      </c>
+      <c r="B19" t="n">
+        <v>66.19</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.41072</v>
+      </c>
+      <c r="D19" t="n">
+        <v>718.857</v>
+      </c>
+      <c r="E19" t="n">
+        <v>37.01079653398823</v>
+      </c>
+      <c r="F19" t="n">
+        <v>66.4396</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.406</v>
+      </c>
+      <c r="H19" t="n">
+        <v>8</v>
+      </c>
+      <c r="I19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.2496000000000009</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>6 6 20</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>29</v>
+      </c>
+      <c r="B20" t="n">
+        <v>67.541</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.38576</v>
+      </c>
+      <c r="D20" t="n">
+        <v>735.1900000000001</v>
+      </c>
+      <c r="E20" t="n">
+        <v>37.85171112449737</v>
+      </c>
+      <c r="F20" t="n">
+        <v>67.5258</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.386</v>
+      </c>
+      <c r="H20" t="n">
+        <v>8</v>
+      </c>
+      <c r="I20" t="n">
+        <v>8</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.015199999999993</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0 0 30</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>31</v>
+      </c>
+      <c r="B21" t="n">
+        <v>68.72799999999999</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.3647</v>
+      </c>
+      <c r="D21" t="n">
+        <v>708.524</v>
+      </c>
+      <c r="E21" t="n">
+        <v>36.47879564843561</v>
+      </c>
+      <c r="F21" t="n">
+        <v>68.9388</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.361</v>
+      </c>
+      <c r="H21" t="n">
+        <v>8</v>
+      </c>
+      <c r="I21" t="n">
+        <v>8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.2108000000000061</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2 0 7</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>35</v>
+      </c>
+      <c r="B22" t="n">
+        <v>74.294</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.27563</v>
+      </c>
+      <c r="D22" t="n">
+        <v>724.2380000000001</v>
+      </c>
+      <c r="E22" t="n">
+        <v>37.28784064171674</v>
+      </c>
+      <c r="F22" t="n">
+        <v>74.4939</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.2727</v>
+      </c>
+      <c r="H22" t="n">
+        <v>57</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5.705705705705705</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.1998999999999995</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2 0 8</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Covellite</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>36</v>
+      </c>
+      <c r="B23" t="n">
+        <v>74.539</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.27203</v>
+      </c>
+      <c r="D23" t="n">
+        <v>731.2859999999999</v>
+      </c>
+      <c r="E23" t="n">
+        <v>37.65071127380566</v>
+      </c>
+      <c r="F23" t="n">
+        <v>74.4939</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.2727</v>
+      </c>
+      <c r="H23" t="n">
+        <v>57</v>
+      </c>
+      <c r="I23" t="n">
+        <v>5.705705705705705</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.04510000000000502</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2 0 8</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Covellite</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>38</v>
+      </c>
+      <c r="B24" t="n">
+        <v>76.46299999999999</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1.24475</v>
+      </c>
+      <c r="D24" t="n">
+        <v>684.476</v>
+      </c>
+      <c r="E24" t="n">
+        <v>35.24066951896987</v>
+      </c>
+      <c r="F24" t="n">
+        <v>76.73350000000001</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="H24" t="n">
+        <v>12</v>
+      </c>
+      <c r="I24" t="n">
+        <v>12</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.2705000000000126</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>6 0 31</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>39</v>
+      </c>
+      <c r="B25" t="n">
+        <v>76.995</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.23747</v>
+      </c>
+      <c r="D25" t="n">
+        <v>677.048</v>
+      </c>
+      <c r="E25" t="n">
+        <v>34.8582343522337</v>
+      </c>
+      <c r="F25" t="n">
+        <v>76.73350000000001</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="H25" t="n">
+        <v>12</v>
+      </c>
+      <c r="I25" t="n">
+        <v>12</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.2614999999999981</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>6 0 31</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>41</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79.36799999999999</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.20632</v>
+      </c>
+      <c r="D26" t="n">
+        <v>703.619</v>
+      </c>
+      <c r="E26" t="n">
+        <v>36.22625869463366</v>
+      </c>
+      <c r="F26" t="n">
+        <v>79.6553</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.2027</v>
+      </c>
+      <c r="H26" t="n">
+        <v>53</v>
+      </c>
+      <c r="I26" t="n">
+        <v>5.305305305305305</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.2873000000000019</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2 1 3</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Covellite</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
@@ -22578,9 +28076,670 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Peak_ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Detected_2theta</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Detected_d</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Experimental_Intensity</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Experimental_Relative_Intensity</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Nearest_Reference_2theta</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Nearest_Phase</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Nearest_Reference_Card</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Nearest_Difference</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B2" t="n">
+        <v>40.121</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2.24569</v>
+      </c>
+      <c r="D2" t="n">
+        <v>663.2859999999999</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.14968928429843</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.2897</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.8312999999999988</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B3" t="n">
+        <v>40.735</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2.21325</v>
+      </c>
+      <c r="D3" t="n">
+        <v>664.524</v>
+      </c>
+      <c r="E3" t="n">
+        <v>34.21342847875446</v>
+      </c>
+      <c r="F3" t="n">
+        <v>41.2844</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0.5493999999999986</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B4" t="n">
+        <v>41.881</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2.15531</v>
+      </c>
+      <c r="D4" t="n">
+        <v>675.333</v>
+      </c>
+      <c r="E4" t="n">
+        <v>34.76993651823363</v>
+      </c>
+      <c r="F4" t="n">
+        <v>41.2844</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.5966000000000022</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B5" t="n">
+        <v>43.006</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2.10148</v>
+      </c>
+      <c r="D5" t="n">
+        <v>711.476</v>
+      </c>
+      <c r="E5" t="n">
+        <v>36.63078119127422</v>
+      </c>
+      <c r="F5" t="n">
+        <v>42.5477</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.4583000000000013</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B6" t="n">
+        <v>46.853</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.9375</v>
+      </c>
+      <c r="D6" t="n">
+        <v>770.7619999999999</v>
+      </c>
+      <c r="E6" t="n">
+        <v>39.6831575099496</v>
+      </c>
+      <c r="F6" t="n">
+        <v>46.158</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.6950000000000003</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>50.598</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.80254</v>
+      </c>
+      <c r="D7" t="n">
+        <v>773.095</v>
+      </c>
+      <c r="E7" t="n">
+        <v>39.80327345556019</v>
+      </c>
+      <c r="F7" t="n">
+        <v>50.0775</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0.5204999999999984</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>55.877</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.6441</v>
+      </c>
+      <c r="D8" t="n">
+        <v>749.095</v>
+      </c>
+      <c r="E8" t="n">
+        <v>38.56761863573411</v>
+      </c>
+      <c r="F8" t="n">
+        <v>56.7051</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0.8280999999999992</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>22</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57.351</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.60531</v>
+      </c>
+      <c r="D9" t="n">
+        <v>827.2859999999999</v>
+      </c>
+      <c r="E9" t="n">
+        <v>42.59333055310999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>56.7051</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0.6458999999999975</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>24</v>
+      </c>
+      <c r="B10" t="n">
+        <v>61.648</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.50332</v>
+      </c>
+      <c r="D10" t="n">
+        <v>760.2380000000001</v>
+      </c>
+      <c r="E10" t="n">
+        <v>39.14132287145586</v>
+      </c>
+      <c r="F10" t="n">
+        <v>63.0584</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.410399999999996</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>25</v>
+      </c>
+      <c r="B11" t="n">
+        <v>62.302</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.48908</v>
+      </c>
+      <c r="D11" t="n">
+        <v>740.667</v>
+      </c>
+      <c r="E11" t="n">
+        <v>38.13369785150518</v>
+      </c>
+      <c r="F11" t="n">
+        <v>63.0584</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.7563999999999993</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>30</v>
+      </c>
+      <c r="B12" t="n">
+        <v>67.95</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.37841</v>
+      </c>
+      <c r="D12" t="n">
+        <v>721.905</v>
+      </c>
+      <c r="E12" t="n">
+        <v>37.16772469610614</v>
+      </c>
+      <c r="F12" t="n">
+        <v>67.5258</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.424199999999999</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>32</v>
+      </c>
+      <c r="B13" t="n">
+        <v>70.16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.3403</v>
+      </c>
+      <c r="D13" t="n">
+        <v>743.2859999999999</v>
+      </c>
+      <c r="E13" t="n">
+        <v>38.2685386837187</v>
+      </c>
+      <c r="F13" t="n">
+        <v>69.749</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.4110000000000014</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>33</v>
+      </c>
+      <c r="B14" t="n">
+        <v>71.797</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.31372</v>
+      </c>
+      <c r="D14" t="n">
+        <v>693.571</v>
+      </c>
+      <c r="E14" t="n">
+        <v>35.70893121006647</v>
+      </c>
+      <c r="F14" t="n">
+        <v>71.3383</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.4586999999999932</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>34</v>
+      </c>
+      <c r="B15" t="n">
+        <v>73.782</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.2832</v>
+      </c>
+      <c r="D15" t="n">
+        <v>729.333</v>
+      </c>
+      <c r="E15" t="n">
+        <v>37.55015986284231</v>
+      </c>
+      <c r="F15" t="n">
+        <v>74.4939</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.7119</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>37</v>
+      </c>
+      <c r="B16" t="n">
+        <v>75.971</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.25157</v>
+      </c>
+      <c r="D16" t="n">
+        <v>668.667</v>
+      </c>
+      <c r="E16" t="n">
+        <v>34.42673339202694</v>
+      </c>
+      <c r="F16" t="n">
+        <v>76.73350000000001</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0.7625000000000028</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>40</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78.161</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.2219</v>
+      </c>
+      <c r="D17" t="n">
+        <v>704.476</v>
+      </c>
+      <c r="E17" t="n">
+        <v>36.27038186882495</v>
+      </c>
+      <c r="F17" t="n">
+        <v>77.37909999999999</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>CuCl</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>000822117</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0.7819000000000074</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22591,7 +28750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22654,130 +28813,169 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>000752233</t>
+          <t>000360380</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu39S28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Covellite</t>
+          <t>Spionkopite</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu39S28</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1529666666666672</v>
+        <v>0.1444000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>0.258499999999998</v>
+        <v>0.2705000000000126</v>
       </c>
       <c r="H2" t="n">
-        <v>386.9196669910261</v>
+        <v>667.9302781767913</v>
       </c>
       <c r="I2" t="n">
-        <v>100</v>
+        <v>41.46341463414634</v>
       </c>
       <c r="J2" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="K2" t="n">
-        <v>40</v>
+        <v>54.83870967741935</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000752233</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Djurleite</t>
+          <t>Covellite</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1501666666666649</v>
+        <v>0.1493800000000011</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2071999999999967</v>
+        <v>0.2873000000000019</v>
       </c>
       <c r="H3" t="n">
-        <v>175.6762378429586</v>
+        <v>534.3352434497424</v>
       </c>
       <c r="I3" t="n">
-        <v>50</v>
+        <v>24.39024390243902</v>
       </c>
       <c r="J3" t="n">
-        <v>116</v>
+        <v>15</v>
       </c>
       <c r="K3" t="n">
-        <v>2.586206896551724</v>
+        <v>66.66666666666666</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>000360380</t>
+          <t>000711383</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cu39S28</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spionkopite</t>
+          <t>Djurleite</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cu39S28</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="E4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1251499999999992</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.2071999999999967</v>
+      </c>
+      <c r="H4" t="n">
+        <v>351.93601367458</v>
+      </c>
+      <c r="I4" t="n">
+        <v>19.51219512195122</v>
+      </c>
+      <c r="J4" t="n">
+        <v>116</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6.896551724137931</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>000822117</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CuCl</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CuCl</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>2</v>
       </c>
-      <c r="F4" t="n">
-        <v>0.1191499999999976</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.2326999999999941</v>
-      </c>
-      <c r="H4" t="n">
-        <v>121.8345355225018</v>
-      </c>
-      <c r="I4" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="J4" t="n">
-        <v>31</v>
-      </c>
-      <c r="K4" t="n">
-        <v>6.451612903225806</v>
+      <c r="F5" t="n">
+        <v>0.06325000000000358</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.1110000000000042</v>
+      </c>
+      <c r="H5" t="n">
+        <v>70.38331042223355</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.878048780487805</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/XRD_Results/CuS B1_CuS_XRD_Analysis.xlsx
+++ b/XRD_Results/CuS B1_CuS_XRD_Analysis.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,7 +469,7 @@
         <v>807.952</v>
       </c>
       <c r="E2" t="n">
-        <v>123.8395011655014</v>
+        <v>116.1905314685312</v>
       </c>
       <c r="F2" t="n">
         <v>41.59790762450509</v>
@@ -489,7 +489,7 @@
         <v>1237.81</v>
       </c>
       <c r="E3" t="n">
-        <v>555.7744685314699</v>
+        <v>555.4838181818163</v>
       </c>
       <c r="F3" t="n">
         <v>63.72941218870508</v>
@@ -500,19 +500,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>30.606</v>
+        <v>32.202</v>
       </c>
       <c r="C4" t="n">
-        <v>2.91866</v>
+        <v>2.77754</v>
       </c>
       <c r="D4" t="n">
-        <v>736.524</v>
+        <v>1366.38</v>
       </c>
       <c r="E4" t="n">
-        <v>30.27249417249436</v>
+        <v>732.5335034965012</v>
       </c>
       <c r="F4" t="n">
-        <v>37.92039293823271</v>
+        <v>70.3489180297484</v>
       </c>
     </row>
     <row r="5">
@@ -520,19 +520,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>32.202</v>
+        <v>38.996</v>
       </c>
       <c r="C5" t="n">
-        <v>2.77754</v>
+        <v>2.30787</v>
       </c>
       <c r="D5" t="n">
-        <v>1366.38</v>
+        <v>691.2859999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>738.8189720279742</v>
+        <v>77.24064335664309</v>
       </c>
       <c r="F5" t="n">
-        <v>70.3489180297484</v>
+        <v>35.59128657409553</v>
       </c>
     </row>
     <row r="6">
@@ -540,19 +540,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>35.394</v>
+        <v>48.183</v>
       </c>
       <c r="C6" t="n">
-        <v>2.53401</v>
+        <v>1.88708</v>
       </c>
       <c r="D6" t="n">
-        <v>655.7619999999999</v>
+        <v>1942.29</v>
       </c>
       <c r="E6" t="n">
-        <v>35.3962331002333</v>
+        <v>1306.847678321674</v>
       </c>
       <c r="F6" t="n">
-        <v>33.76231149828295</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -560,19 +560,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>36.315</v>
+        <v>52.849</v>
       </c>
       <c r="C7" t="n">
-        <v>2.47184</v>
+        <v>1.73095</v>
       </c>
       <c r="D7" t="n">
-        <v>655.524</v>
+        <v>1000</v>
       </c>
       <c r="E7" t="n">
-        <v>35.70010256410251</v>
+        <v>260.6997972027964</v>
       </c>
       <c r="F7" t="n">
-        <v>33.75005792131968</v>
+        <v>51.4856174927534</v>
       </c>
     </row>
     <row r="8">
@@ -580,19 +580,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>37.932</v>
+        <v>59.315</v>
       </c>
       <c r="C8" t="n">
-        <v>2.37013</v>
+        <v>1.55675</v>
       </c>
       <c r="D8" t="n">
-        <v>671.571</v>
+        <v>1158.67</v>
       </c>
       <c r="E8" t="n">
-        <v>37.57773193473213</v>
+        <v>446.4071258741246</v>
       </c>
       <c r="F8" t="n">
-        <v>34.5762476252259</v>
+        <v>59.65484042032858</v>
       </c>
     </row>
     <row r="9">
@@ -600,19 +600,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>39.016</v>
+        <v>63.101</v>
       </c>
       <c r="C9" t="n">
-        <v>2.30671</v>
+        <v>1.47216</v>
       </c>
       <c r="D9" t="n">
-        <v>704.095</v>
+        <v>756.2859999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>81.61939393939406</v>
+        <v>61.12137762237762</v>
       </c>
       <c r="F9" t="n">
-        <v>36.25076584856021</v>
+        <v>38.93785171112449</v>
       </c>
     </row>
     <row r="10">
@@ -620,19 +620,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>40.121</v>
+        <v>70.14</v>
       </c>
       <c r="C10" t="n">
-        <v>2.24569</v>
+        <v>1.34065</v>
       </c>
       <c r="D10" t="n">
-        <v>663.2859999999999</v>
+        <v>732.571</v>
       </c>
       <c r="E10" t="n">
-        <v>32.60576923076928</v>
+        <v>56.04148951048933</v>
       </c>
       <c r="F10" t="n">
-        <v>34.14968928429843</v>
+        <v>37.71687029228386</v>
       </c>
     </row>
     <row r="11">
@@ -640,639 +640,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>40.735</v>
+        <v>74.51900000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>2.21325</v>
+        <v>1.27233</v>
       </c>
       <c r="D11" t="n">
-        <v>664.524</v>
+        <v>717.2859999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>37.67823076923094</v>
+        <v>75.38560839160812</v>
       </c>
       <c r="F11" t="n">
-        <v>34.21342847875446</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="n">
-        <v>41.267</v>
-      </c>
-      <c r="C12" t="n">
-        <v>2.18594</v>
-      </c>
-      <c r="D12" t="n">
-        <v>676.905</v>
-      </c>
-      <c r="E12" t="n">
-        <v>39.03099067599089</v>
-      </c>
-      <c r="F12" t="n">
-        <v>34.85087190893224</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="n">
-        <v>41.881</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2.15531</v>
-      </c>
-      <c r="D13" t="n">
-        <v>675.333</v>
-      </c>
-      <c r="E13" t="n">
-        <v>36.55203030303051</v>
-      </c>
-      <c r="F13" t="n">
-        <v>34.76993651823363</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="n">
-        <v>43.006</v>
-      </c>
-      <c r="C14" t="n">
-        <v>2.10148</v>
-      </c>
-      <c r="D14" t="n">
-        <v>711.476</v>
-      </c>
-      <c r="E14" t="n">
-        <v>40.65626573426584</v>
-      </c>
-      <c r="F14" t="n">
-        <v>36.63078119127422</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="n">
-        <v>43.866</v>
-      </c>
-      <c r="C15" t="n">
-        <v>2.06228</v>
-      </c>
-      <c r="D15" t="n">
-        <v>708.8099999999999</v>
-      </c>
-      <c r="E15" t="n">
-        <v>49.50725641025645</v>
-      </c>
-      <c r="F15" t="n">
-        <v>36.49352053503853</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="n">
-        <v>45.973</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1.97251</v>
-      </c>
-      <c r="D16" t="n">
-        <v>709.143</v>
-      </c>
-      <c r="E16" t="n">
-        <v>33.30796736596744</v>
-      </c>
-      <c r="F16" t="n">
-        <v>36.51066524566362</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="n">
-        <v>46.853</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1.9375</v>
-      </c>
-      <c r="D17" t="n">
-        <v>770.7619999999999</v>
-      </c>
-      <c r="E17" t="n">
-        <v>34.60022843822844</v>
-      </c>
-      <c r="F17" t="n">
-        <v>39.6831575099496</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="n">
-        <v>48.183</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1.88708</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1942.29</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1312.670331002334</v>
-      </c>
-      <c r="F18" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="n">
-        <v>50.598</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1.80254</v>
-      </c>
-      <c r="D19" t="n">
-        <v>773.095</v>
-      </c>
-      <c r="E19" t="n">
-        <v>39.30611188811201</v>
-      </c>
-      <c r="F19" t="n">
-        <v>39.80327345556019</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="n">
-        <v>52.849</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1.73095</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E20" t="n">
-        <v>269.3306200466208</v>
-      </c>
-      <c r="F20" t="n">
-        <v>51.4856174927534</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="n">
-        <v>54.629</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1.67867</v>
-      </c>
-      <c r="D21" t="n">
-        <v>752.2859999999999</v>
-      </c>
-      <c r="E21" t="n">
-        <v>29.98480419580437</v>
-      </c>
-      <c r="F21" t="n">
-        <v>38.73190924115348</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="n">
-        <v>55.877</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1.6441</v>
-      </c>
-      <c r="D22" t="n">
-        <v>749.095</v>
-      </c>
-      <c r="E22" t="n">
-        <v>38.98323310023318</v>
-      </c>
-      <c r="F22" t="n">
-        <v>38.56761863573411</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="n">
-        <v>57.351</v>
-      </c>
-      <c r="C23" t="n">
-        <v>1.60531</v>
-      </c>
-      <c r="D23" t="n">
-        <v>827.2859999999999</v>
-      </c>
-      <c r="E23" t="n">
-        <v>44.05834032634039</v>
-      </c>
-      <c r="F23" t="n">
-        <v>42.59333055310999</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="n">
-        <v>59.335</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1.55626</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1160.67</v>
-      </c>
-      <c r="E24" t="n">
-        <v>458.3228881118894</v>
-      </c>
-      <c r="F24" t="n">
-        <v>59.7578116553141</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="n">
-        <v>61.648</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1.50332</v>
-      </c>
-      <c r="D25" t="n">
-        <v>760.2380000000001</v>
-      </c>
-      <c r="E25" t="n">
-        <v>39.67465734265761</v>
-      </c>
-      <c r="F25" t="n">
-        <v>39.14132287145586</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="n">
-        <v>62.302</v>
-      </c>
-      <c r="C26" t="n">
-        <v>1.48908</v>
-      </c>
-      <c r="D26" t="n">
-        <v>740.667</v>
-      </c>
-      <c r="E26" t="n">
-        <v>49.22194172494176</v>
-      </c>
-      <c r="F26" t="n">
-        <v>38.13369785150518</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="n">
-        <v>63.101</v>
-      </c>
-      <c r="C27" t="n">
-        <v>1.47216</v>
-      </c>
-      <c r="D27" t="n">
-        <v>756.2859999999999</v>
-      </c>
-      <c r="E27" t="n">
-        <v>68.22245687645704</v>
-      </c>
-      <c r="F27" t="n">
-        <v>38.93785171112449</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="n">
-        <v>65.536</v>
-      </c>
-      <c r="C28" t="n">
-        <v>1.42323</v>
-      </c>
-      <c r="D28" t="n">
-        <v>711.524</v>
-      </c>
-      <c r="E28" t="n">
-        <v>42.85821445221461</v>
-      </c>
-      <c r="F28" t="n">
-        <v>36.63325250091387</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="n">
-        <v>66.19</v>
-      </c>
-      <c r="C29" t="n">
-        <v>1.41072</v>
-      </c>
-      <c r="D29" t="n">
-        <v>718.857</v>
-      </c>
-      <c r="E29" t="n">
-        <v>29.93228205128219</v>
-      </c>
-      <c r="F29" t="n">
-        <v>37.01079653398823</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="n">
-        <v>67.541</v>
-      </c>
-      <c r="C30" t="n">
-        <v>1.38576</v>
-      </c>
-      <c r="D30" t="n">
-        <v>735.1900000000001</v>
-      </c>
-      <c r="E30" t="n">
-        <v>54.91938694638702</v>
-      </c>
-      <c r="F30" t="n">
-        <v>37.85171112449737</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="n">
-        <v>67.95</v>
-      </c>
-      <c r="C31" t="n">
-        <v>1.37841</v>
-      </c>
-      <c r="D31" t="n">
-        <v>721.905</v>
-      </c>
-      <c r="E31" t="n">
-        <v>47.02834965034981</v>
-      </c>
-      <c r="F31" t="n">
-        <v>37.16772469610614</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="n">
-        <v>68.72799999999999</v>
-      </c>
-      <c r="C32" t="n">
-        <v>1.3647</v>
-      </c>
-      <c r="D32" t="n">
-        <v>708.524</v>
-      </c>
-      <c r="E32" t="n">
-        <v>30.52301398601412</v>
-      </c>
-      <c r="F32" t="n">
-        <v>36.47879564843561</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="n">
-        <v>70.16</v>
-      </c>
-      <c r="C33" t="n">
-        <v>1.3403</v>
-      </c>
-      <c r="D33" t="n">
-        <v>743.2859999999999</v>
-      </c>
-      <c r="E33" t="n">
-        <v>64.25235431235456</v>
-      </c>
-      <c r="F33" t="n">
-        <v>38.2685386837187</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="n">
-        <v>71.797</v>
-      </c>
-      <c r="C34" t="n">
-        <v>1.31372</v>
-      </c>
-      <c r="D34" t="n">
-        <v>693.571</v>
-      </c>
-      <c r="E34" t="n">
-        <v>38.92793006993008</v>
-      </c>
-      <c r="F34" t="n">
-        <v>35.70893121006647</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="n">
-        <v>73.782</v>
-      </c>
-      <c r="C35" t="n">
-        <v>1.2832</v>
-      </c>
-      <c r="D35" t="n">
-        <v>729.333</v>
-      </c>
-      <c r="E35" t="n">
-        <v>51.68265734265742</v>
-      </c>
-      <c r="F35" t="n">
-        <v>37.55015986284231</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="n">
-        <v>74.294</v>
-      </c>
-      <c r="C36" t="n">
-        <v>1.27563</v>
-      </c>
-      <c r="D36" t="n">
-        <v>724.2380000000001</v>
-      </c>
-      <c r="E36" t="n">
-        <v>30.23593240093248</v>
-      </c>
-      <c r="F36" t="n">
-        <v>37.28784064171674</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="n">
-        <v>74.539</v>
-      </c>
-      <c r="C37" t="n">
-        <v>1.27203</v>
-      </c>
-      <c r="D37" t="n">
-        <v>731.2859999999999</v>
-      </c>
-      <c r="E37" t="n">
-        <v>82.93523310023329</v>
-      </c>
-      <c r="F37" t="n">
-        <v>37.65071127380566</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="n">
-        <v>75.971</v>
-      </c>
-      <c r="C38" t="n">
-        <v>1.25157</v>
-      </c>
-      <c r="D38" t="n">
-        <v>668.667</v>
-      </c>
-      <c r="E38" t="n">
-        <v>31.29283216783222</v>
-      </c>
-      <c r="F38" t="n">
-        <v>34.42673339202694</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="n">
-        <v>76.46299999999999</v>
-      </c>
-      <c r="C39" t="n">
-        <v>1.24475</v>
-      </c>
-      <c r="D39" t="n">
-        <v>684.476</v>
-      </c>
-      <c r="E39" t="n">
-        <v>33.68230769230775</v>
-      </c>
-      <c r="F39" t="n">
-        <v>35.24066951896987</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="n">
-        <v>76.995</v>
-      </c>
-      <c r="C40" t="n">
-        <v>1.23747</v>
-      </c>
-      <c r="D40" t="n">
-        <v>677.048</v>
-      </c>
-      <c r="E40" t="n">
-        <v>31.7052890442892</v>
-      </c>
-      <c r="F40" t="n">
-        <v>34.8582343522337</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="n">
-        <v>78.161</v>
-      </c>
-      <c r="C41" t="n">
-        <v>1.2219</v>
-      </c>
-      <c r="D41" t="n">
-        <v>704.476</v>
-      </c>
-      <c r="E41" t="n">
-        <v>50.68701631701822</v>
-      </c>
-      <c r="F41" t="n">
-        <v>36.27038186882495</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="n">
-        <v>79.36799999999999</v>
-      </c>
-      <c r="C42" t="n">
-        <v>1.20632</v>
-      </c>
-      <c r="D42" t="n">
-        <v>703.619</v>
-      </c>
-      <c r="E42" t="n">
-        <v>41.84309557109566</v>
-      </c>
-      <c r="F42" t="n">
-        <v>36.22625869463366</v>
+        <v>36.92991262890711</v>
       </c>
     </row>
   </sheetData>
@@ -21386,7 +20766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q76"/>
+  <dimension ref="A1:R33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21475,6 +20855,11 @@
           <t>Status</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Phase_Priority</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -21540,6 +20925,9 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -21605,6 +20993,9 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R3" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -21670,6 +21061,9 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -21735,6 +21129,9 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -21800,6 +21197,9 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R6" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -21865,6 +21265,9 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R7" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -21930,6 +21333,9 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R8" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -21995,6 +21401,9 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R9" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -22060,6 +21469,9 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R10" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -22125,6 +21537,9 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R11" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -22190,41 +21605,44 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R12" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>30.606</v>
+        <v>32.202</v>
       </c>
       <c r="C13" t="n">
-        <v>2.91866</v>
+        <v>2.77754</v>
       </c>
       <c r="D13" t="n">
-        <v>736.524</v>
+        <v>1366.38</v>
       </c>
       <c r="E13" t="n">
-        <v>37.92039293823271</v>
+        <v>70.3489180297484</v>
       </c>
       <c r="F13" t="n">
-        <v>30.5264</v>
+        <v>32.2076</v>
       </c>
       <c r="G13" t="n">
-        <v>2.926</v>
+        <v>2.777</v>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="J13" t="n">
-        <v>0.07960000000000278</v>
+        <v>0.00560000000000116</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>3 1 12</t>
+          <t>6 0 8</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -22254,6 +21672,9 @@
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -22261,35 +21682,35 @@
         <v>3</v>
       </c>
       <c r="B14" t="n">
-        <v>30.606</v>
+        <v>32.202</v>
       </c>
       <c r="C14" t="n">
-        <v>2.91866</v>
+        <v>2.77754</v>
       </c>
       <c r="D14" t="n">
-        <v>736.524</v>
+        <v>1366.38</v>
       </c>
       <c r="E14" t="n">
-        <v>37.92039293823271</v>
+        <v>70.3489180297484</v>
       </c>
       <c r="F14" t="n">
-        <v>30.7772</v>
+        <v>32.0508</v>
       </c>
       <c r="G14" t="n">
-        <v>2.9027</v>
+        <v>2.7902</v>
       </c>
       <c r="H14" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I14" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1711999999999989</v>
+        <v>0.1511999999999958</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-3 5 1</t>
+          <t>2 5 2</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -22319,6 +21740,9 @@
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R14" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -22326,35 +21750,35 @@
         <v>3</v>
       </c>
       <c r="B15" t="n">
-        <v>30.606</v>
+        <v>32.202</v>
       </c>
       <c r="C15" t="n">
-        <v>2.91866</v>
+        <v>2.77754</v>
       </c>
       <c r="D15" t="n">
-        <v>736.524</v>
+        <v>1366.38</v>
       </c>
       <c r="E15" t="n">
-        <v>37.92039293823271</v>
+        <v>70.3489180297484</v>
       </c>
       <c r="F15" t="n">
-        <v>30.7772</v>
+        <v>32.0508</v>
       </c>
       <c r="G15" t="n">
-        <v>2.9027</v>
+        <v>2.7902</v>
       </c>
       <c r="H15" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I15" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1711999999999989</v>
+        <v>0.1511999999999958</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>3 5 1</t>
+          <t>4 5 1</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -22384,6 +21808,9 @@
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R15" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -22391,55 +21818,55 @@
         <v>3</v>
       </c>
       <c r="B16" t="n">
-        <v>30.606</v>
+        <v>32.202</v>
       </c>
       <c r="C16" t="n">
-        <v>2.91866</v>
+        <v>2.77754</v>
       </c>
       <c r="D16" t="n">
-        <v>736.524</v>
+        <v>1366.38</v>
       </c>
       <c r="E16" t="n">
-        <v>37.92039293823271</v>
+        <v>70.3489180297484</v>
       </c>
       <c r="F16" t="n">
-        <v>30.3755</v>
+        <v>31.982</v>
       </c>
       <c r="G16" t="n">
-        <v>2.9402</v>
+        <v>2.7961</v>
       </c>
       <c r="H16" t="n">
-        <v>8</v>
+        <v>999</v>
       </c>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2305000000000028</v>
+        <v>0.2199999999999989</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-3 2 4</t>
+          <t>1 0 3</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Djurleite</t>
+          <t>Covellite</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000752233</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -22450,106 +21877,112 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B17" t="n">
-        <v>30.606</v>
+        <v>38.996</v>
       </c>
       <c r="C17" t="n">
-        <v>2.91866</v>
+        <v>2.30787</v>
       </c>
       <c r="D17" t="n">
-        <v>736.524</v>
+        <v>691.2859999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>37.92039293823271</v>
+        <v>35.59128657409553</v>
       </c>
       <c r="F17" t="n">
-        <v>30.3755</v>
+        <v>39.0597</v>
       </c>
       <c r="G17" t="n">
-        <v>2.9402</v>
+        <v>2.3042</v>
       </c>
       <c r="H17" t="n">
-        <v>8</v>
+        <v>126</v>
       </c>
       <c r="I17" t="n">
-        <v>8</v>
+        <v>12.61261261261261</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2305000000000028</v>
+        <v>0.0636999999999972</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>3 2 4</t>
+          <t>1 0 5</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Djurleite</t>
+          <t>Covellite</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000752233</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B18" t="n">
-        <v>30.606</v>
+        <v>38.996</v>
       </c>
       <c r="C18" t="n">
-        <v>2.91866</v>
+        <v>2.30787</v>
       </c>
       <c r="D18" t="n">
-        <v>736.524</v>
+        <v>691.2859999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>37.92039293823271</v>
+        <v>35.59128657409553</v>
       </c>
       <c r="F18" t="n">
-        <v>30.8969</v>
+        <v>38.8318</v>
       </c>
       <c r="G18" t="n">
-        <v>2.8918</v>
+        <v>2.3172</v>
       </c>
       <c r="H18" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="I18" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="J18" t="n">
-        <v>0.290899999999997</v>
+        <v>0.164200000000001</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-5 3 3</t>
+          <t>-5 2 5</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -22573,77 +22006,83 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" t="n">
+        <v>38.996</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2.30787</v>
+      </c>
+      <c r="D19" t="n">
+        <v>691.2859999999999</v>
+      </c>
+      <c r="E19" t="n">
+        <v>35.59128657409553</v>
+      </c>
+      <c r="F19" t="n">
+        <v>38.8318</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.3172</v>
+      </c>
+      <c r="H19" t="n">
+        <v>6</v>
+      </c>
+      <c r="I19" t="n">
+        <v>6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.164200000000001</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>5 4 4</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
         <v>3</v>
       </c>
-      <c r="B19" t="n">
-        <v>30.606</v>
-      </c>
-      <c r="C19" t="n">
-        <v>2.91866</v>
-      </c>
-      <c r="D19" t="n">
-        <v>736.524</v>
-      </c>
-      <c r="E19" t="n">
-        <v>37.92039293823271</v>
-      </c>
-      <c r="F19" t="n">
-        <v>30.8969</v>
-      </c>
-      <c r="G19" t="n">
-        <v>2.8918</v>
-      </c>
-      <c r="H19" t="n">
-        <v>21</v>
-      </c>
-      <c r="I19" t="n">
-        <v>21</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.290899999999997</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>6 4 1</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Djurleite</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>000711383</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>7</v>
-      </c>
       <c r="Q19" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R19" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -22651,64 +22090,67 @@
         <v>4</v>
       </c>
       <c r="B20" t="n">
-        <v>32.202</v>
+        <v>38.996</v>
       </c>
       <c r="C20" t="n">
-        <v>2.77754</v>
+        <v>2.30787</v>
       </c>
       <c r="D20" t="n">
-        <v>1366.38</v>
+        <v>691.2859999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>70.3489180297484</v>
+        <v>35.59128657409553</v>
       </c>
       <c r="F20" t="n">
-        <v>32.2076</v>
+        <v>39.1604</v>
       </c>
       <c r="G20" t="n">
-        <v>2.777</v>
+        <v>2.2985</v>
       </c>
       <c r="H20" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="I20" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="J20" t="n">
-        <v>0.00560000000000116</v>
+        <v>0.1644000000000005</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>6 0 8</t>
+          <t>-4 6 2</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Cu39S28</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Spionkopite</t>
+          <t>Djurleite</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Cu39S28</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>000360380</t>
+          <t>000711383</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -22716,22 +22158,22 @@
         <v>4</v>
       </c>
       <c r="B21" t="n">
-        <v>32.202</v>
+        <v>38.996</v>
       </c>
       <c r="C21" t="n">
-        <v>2.77754</v>
+        <v>2.30787</v>
       </c>
       <c r="D21" t="n">
-        <v>1366.38</v>
+        <v>691.2859999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>70.3489180297484</v>
+        <v>35.59128657409553</v>
       </c>
       <c r="F21" t="n">
-        <v>32.0508</v>
+        <v>39.1604</v>
       </c>
       <c r="G21" t="n">
-        <v>2.7902</v>
+        <v>2.2985</v>
       </c>
       <c r="H21" t="n">
         <v>6</v>
@@ -22740,11 +22182,11 @@
         <v>6</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1511999999999958</v>
+        <v>0.1644000000000005</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2 5 2</t>
+          <t>-6 1 5</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -22768,12 +22210,15 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R21" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -22781,64 +22226,67 @@
         <v>4</v>
       </c>
       <c r="B22" t="n">
-        <v>32.202</v>
+        <v>38.996</v>
       </c>
       <c r="C22" t="n">
-        <v>2.77754</v>
+        <v>2.30787</v>
       </c>
       <c r="D22" t="n">
-        <v>1366.38</v>
+        <v>691.2859999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>70.3489180297484</v>
+        <v>35.59128657409553</v>
       </c>
       <c r="F22" t="n">
-        <v>32.0508</v>
+        <v>39.1866</v>
       </c>
       <c r="G22" t="n">
-        <v>2.7902</v>
+        <v>2.297</v>
       </c>
       <c r="H22" t="n">
+        <v>25</v>
+      </c>
+      <c r="I22" t="n">
+        <v>25</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.1905999999999963</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>6 0 13</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
         <v>6</v>
       </c>
-      <c r="I22" t="n">
-        <v>6</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.1511999999999958</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>4 5 1</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Djurleite</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>000711383</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R22" t="n">
         <v>3</v>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
       </c>
     </row>
     <row r="23">
@@ -22846,100 +22294,103 @@
         <v>4</v>
       </c>
       <c r="B23" t="n">
-        <v>32.202</v>
+        <v>38.996</v>
       </c>
       <c r="C23" t="n">
-        <v>2.77754</v>
+        <v>2.30787</v>
       </c>
       <c r="D23" t="n">
-        <v>1366.38</v>
+        <v>691.2859999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>70.3489180297484</v>
+        <v>35.59128657409553</v>
       </c>
       <c r="F23" t="n">
-        <v>31.982</v>
+        <v>38.7261</v>
       </c>
       <c r="G23" t="n">
-        <v>2.7961</v>
+        <v>2.3233</v>
       </c>
       <c r="H23" t="n">
-        <v>999</v>
+        <v>8</v>
       </c>
       <c r="I23" t="n">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2199999999999989</v>
+        <v>0.2698999999999998</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1 0 3</t>
+          <t>-5 6 1</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Covellite</t>
+          <t>Djurleite</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>000752233</t>
+          <t>000711383</t>
         </is>
       </c>
       <c r="P23" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R23" t="n">
         <v>4</v>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B24" t="n">
-        <v>35.394</v>
+        <v>38.996</v>
       </c>
       <c r="C24" t="n">
-        <v>2.53401</v>
+        <v>2.30787</v>
       </c>
       <c r="D24" t="n">
-        <v>655.7619999999999</v>
+        <v>691.2859999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>33.76231149828295</v>
+        <v>35.59128657409553</v>
       </c>
       <c r="F24" t="n">
-        <v>35.4426</v>
+        <v>38.7261</v>
       </c>
       <c r="G24" t="n">
-        <v>2.5306</v>
+        <v>2.3233</v>
       </c>
       <c r="H24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J24" t="n">
-        <v>0.04860000000000042</v>
+        <v>0.2698999999999998</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>-2 6 1</t>
+          <t>5 6 1</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -22963,48 +22414,51 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R24" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B25" t="n">
-        <v>35.394</v>
+        <v>38.996</v>
       </c>
       <c r="C25" t="n">
-        <v>2.53401</v>
+        <v>2.30787</v>
       </c>
       <c r="D25" t="n">
-        <v>655.7619999999999</v>
+        <v>691.2859999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>33.76231149828295</v>
+        <v>35.59128657409553</v>
       </c>
       <c r="F25" t="n">
-        <v>35.4426</v>
+        <v>39.2897</v>
       </c>
       <c r="G25" t="n">
-        <v>2.5306</v>
+        <v>2.2912</v>
       </c>
       <c r="H25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J25" t="n">
-        <v>0.04860000000000042</v>
+        <v>0.2937000000000012</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2 6 1</t>
+          <t>7 5 2</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -23028,48 +22482,51 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B26" t="n">
-        <v>35.394</v>
+        <v>38.996</v>
       </c>
       <c r="C26" t="n">
-        <v>2.53401</v>
+        <v>2.30787</v>
       </c>
       <c r="D26" t="n">
-        <v>655.7619999999999</v>
+        <v>691.2859999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>33.76231149828295</v>
+        <v>35.59128657409553</v>
       </c>
       <c r="F26" t="n">
-        <v>35.3317</v>
+        <v>39.2897</v>
       </c>
       <c r="G26" t="n">
-        <v>2.5383</v>
+        <v>2.2912</v>
       </c>
       <c r="H26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I26" t="n">
-        <v>7.000000000000001</v>
+        <v>9</v>
       </c>
       <c r="J26" t="n">
-        <v>0.06230000000000047</v>
+        <v>0.2937000000000012</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-2 5 3</t>
+          <t>-7 5 2</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -23093,12 +22550,15 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -23106,64 +22566,67 @@
         <v>5</v>
       </c>
       <c r="B27" t="n">
-        <v>35.394</v>
+        <v>48.183</v>
       </c>
       <c r="C27" t="n">
-        <v>2.53401</v>
+        <v>1.88708</v>
       </c>
       <c r="D27" t="n">
-        <v>655.7619999999999</v>
+        <v>1942.29</v>
       </c>
       <c r="E27" t="n">
-        <v>33.76231149828295</v>
+        <v>100</v>
       </c>
       <c r="F27" t="n">
-        <v>35.3317</v>
+        <v>48.2657</v>
       </c>
       <c r="G27" t="n">
-        <v>2.5383</v>
+        <v>1.884</v>
       </c>
       <c r="H27" t="n">
-        <v>7</v>
+        <v>618</v>
       </c>
       <c r="I27" t="n">
-        <v>7.000000000000001</v>
+        <v>61.86186186186187</v>
       </c>
       <c r="J27" t="n">
-        <v>0.06230000000000047</v>
+        <v>0.08270000000000266</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2 5 3</t>
+          <t>1 1 0</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Djurleite</t>
+          <t>Covellite</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000752233</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -23171,282 +22634,294 @@
         <v>5</v>
       </c>
       <c r="B28" t="n">
-        <v>35.394</v>
+        <v>48.183</v>
       </c>
       <c r="C28" t="n">
-        <v>2.53401</v>
+        <v>1.88708</v>
       </c>
       <c r="D28" t="n">
-        <v>655.7619999999999</v>
+        <v>1942.29</v>
       </c>
       <c r="E28" t="n">
-        <v>33.76231149828295</v>
+        <v>100</v>
       </c>
       <c r="F28" t="n">
-        <v>35.5434</v>
+        <v>48.0177</v>
       </c>
       <c r="G28" t="n">
-        <v>2.5236</v>
+        <v>1.8931</v>
       </c>
       <c r="H28" t="n">
-        <v>16</v>
+        <v>165</v>
       </c>
       <c r="I28" t="n">
-        <v>16</v>
+        <v>16.51651651651652</v>
       </c>
       <c r="J28" t="n">
-        <v>0.1494</v>
+        <v>0.165300000000002</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-5 5 2</t>
+          <t>1 0 7</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Djurleite</t>
+          <t>Covellite</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000752233</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B29" t="n">
-        <v>35.394</v>
+        <v>52.849</v>
       </c>
       <c r="C29" t="n">
-        <v>2.53401</v>
+        <v>1.73095</v>
       </c>
       <c r="D29" t="n">
-        <v>655.7619999999999</v>
+        <v>1000</v>
       </c>
       <c r="E29" t="n">
-        <v>33.76231149828295</v>
+        <v>51.4856174927534</v>
       </c>
       <c r="F29" t="n">
-        <v>35.5434</v>
+        <v>53.0112</v>
       </c>
       <c r="G29" t="n">
-        <v>2.5236</v>
+        <v>1.726</v>
       </c>
       <c r="H29" t="n">
-        <v>16</v>
+        <v>256</v>
       </c>
       <c r="I29" t="n">
-        <v>16</v>
+        <v>25.62562562562562</v>
       </c>
       <c r="J29" t="n">
-        <v>0.1494</v>
+        <v>0.1622000000000057</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>5 5 2</t>
+          <t>1 0 8</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Djurleite</t>
+          <t>Covellite</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000752233</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B30" t="n">
-        <v>35.394</v>
+        <v>52.849</v>
       </c>
       <c r="C30" t="n">
-        <v>2.53401</v>
+        <v>1.73095</v>
       </c>
       <c r="D30" t="n">
-        <v>655.7619999999999</v>
+        <v>1000</v>
       </c>
       <c r="E30" t="n">
-        <v>33.76231149828295</v>
+        <v>51.4856174927534</v>
       </c>
       <c r="F30" t="n">
-        <v>35.0955</v>
+        <v>52.6163</v>
       </c>
       <c r="G30" t="n">
-        <v>2.5548</v>
+        <v>1.738</v>
       </c>
       <c r="H30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J30" t="n">
-        <v>0.2984999999999971</v>
+        <v>0.2326999999999941</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>7 3 3</t>
+          <t>6 6 10</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>Cu39S28</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Djurleite</t>
+          <t>Spionkopite</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>Cu39S28</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000360380</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R30" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B31" t="n">
-        <v>35.394</v>
+        <v>59.315</v>
       </c>
       <c r="C31" t="n">
-        <v>2.53401</v>
+        <v>1.55675</v>
       </c>
       <c r="D31" t="n">
-        <v>655.7619999999999</v>
+        <v>1158.67</v>
       </c>
       <c r="E31" t="n">
-        <v>33.76231149828295</v>
+        <v>59.65484042032858</v>
       </c>
       <c r="F31" t="n">
-        <v>35.0955</v>
+        <v>59.0765</v>
       </c>
       <c r="G31" t="n">
-        <v>2.5548</v>
+        <v>1.5624</v>
       </c>
       <c r="H31" t="n">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="I31" t="n">
-        <v>14</v>
+        <v>10.41041041041041</v>
       </c>
       <c r="J31" t="n">
-        <v>0.2984999999999971</v>
+        <v>0.2384999999999948</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>-8 2 3</t>
+          <t>2 0 3</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Djurleite</t>
+          <t>Covellite</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000752233</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B32" t="n">
-        <v>36.315</v>
+        <v>63.101</v>
       </c>
       <c r="C32" t="n">
-        <v>2.47184</v>
+        <v>1.47216</v>
       </c>
       <c r="D32" t="n">
-        <v>655.524</v>
+        <v>756.2859999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>33.75005792131968</v>
+        <v>38.93785171112449</v>
       </c>
       <c r="F32" t="n">
-        <v>36.2877</v>
+        <v>63.0584</v>
       </c>
       <c r="G32" t="n">
-        <v>2.4736</v>
+        <v>1.473</v>
       </c>
       <c r="H32" t="n">
         <v>15</v>
@@ -23455,31 +22930,31 @@
         <v>15</v>
       </c>
       <c r="J32" t="n">
-        <v>0.02729999999999677</v>
+        <v>0.04260000000000019</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>3 6 1</t>
+          <t>12 0 13</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>Cu39S28</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Djurleite</t>
+          <t>Spionkopite</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>Cu39S28</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000360380</t>
         </is>
       </c>
       <c r="P32" t="n">
@@ -23490,2857 +22965,76 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R32" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B33" t="n">
-        <v>36.315</v>
+        <v>74.51900000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>2.47184</v>
+        <v>1.27233</v>
       </c>
       <c r="D33" t="n">
-        <v>655.524</v>
+        <v>717.2859999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>33.75005792131968</v>
+        <v>36.92991262890711</v>
       </c>
       <c r="F33" t="n">
-        <v>36.2877</v>
+        <v>74.4939</v>
       </c>
       <c r="G33" t="n">
-        <v>2.4736</v>
+        <v>1.2727</v>
       </c>
       <c r="H33" t="n">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="I33" t="n">
-        <v>15</v>
+        <v>5.705705705705705</v>
       </c>
       <c r="J33" t="n">
-        <v>0.02729999999999677</v>
+        <v>0.025100000000009</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>6 4 3</t>
+          <t>2 0 8</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Djurleite</t>
+          <t>Covellite</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000752233</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>6</v>
-      </c>
-      <c r="B34" t="n">
-        <v>36.315</v>
-      </c>
-      <c r="C34" t="n">
-        <v>2.47184</v>
-      </c>
-      <c r="D34" t="n">
-        <v>655.524</v>
-      </c>
-      <c r="E34" t="n">
-        <v>33.75005792131968</v>
-      </c>
-      <c r="F34" t="n">
-        <v>36.3813</v>
-      </c>
-      <c r="G34" t="n">
-        <v>2.4674</v>
-      </c>
-      <c r="H34" t="n">
-        <v>14</v>
-      </c>
-      <c r="I34" t="n">
-        <v>14</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.06630000000000535</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>10 1 2</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Djurleite</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>000711383</t>
-        </is>
-      </c>
-      <c r="P34" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>6</v>
-      </c>
-      <c r="B35" t="n">
-        <v>36.315</v>
-      </c>
-      <c r="C35" t="n">
-        <v>2.47184</v>
-      </c>
-      <c r="D35" t="n">
-        <v>655.524</v>
-      </c>
-      <c r="E35" t="n">
-        <v>33.75005792131968</v>
-      </c>
-      <c r="F35" t="n">
-        <v>36.3813</v>
-      </c>
-      <c r="G35" t="n">
-        <v>2.4674</v>
-      </c>
-      <c r="H35" t="n">
-        <v>14</v>
-      </c>
-      <c r="I35" t="n">
-        <v>14</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0.06630000000000535</v>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>-3 2 5</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Djurleite</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>000711383</t>
-        </is>
-      </c>
-      <c r="P35" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>6</v>
-      </c>
-      <c r="B36" t="n">
-        <v>36.315</v>
-      </c>
-      <c r="C36" t="n">
-        <v>2.47184</v>
-      </c>
-      <c r="D36" t="n">
-        <v>655.524</v>
-      </c>
-      <c r="E36" t="n">
-        <v>33.75005792131968</v>
-      </c>
-      <c r="F36" t="n">
-        <v>36.426</v>
-      </c>
-      <c r="G36" t="n">
-        <v>2.4645</v>
-      </c>
-      <c r="H36" t="n">
-        <v>999</v>
-      </c>
-      <c r="I36" t="n">
-        <v>100</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.1110000000000042</v>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>2 0 0</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>CuCl</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>CuCl</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>000822117</t>
-        </is>
-      </c>
-      <c r="P36" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>6</v>
-      </c>
-      <c r="B37" t="n">
-        <v>36.315</v>
-      </c>
-      <c r="C37" t="n">
-        <v>2.47184</v>
-      </c>
-      <c r="D37" t="n">
-        <v>655.524</v>
-      </c>
-      <c r="E37" t="n">
-        <v>33.75005792131968</v>
-      </c>
-      <c r="F37" t="n">
-        <v>36.1452</v>
-      </c>
-      <c r="G37" t="n">
-        <v>2.483</v>
-      </c>
-      <c r="H37" t="n">
-        <v>5</v>
-      </c>
-      <c r="I37" t="n">
-        <v>5</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0.1697999999999951</v>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>6 0 11</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Spionkopite</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="P37" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>6</v>
-      </c>
-      <c r="B38" t="n">
-        <v>36.315</v>
-      </c>
-      <c r="C38" t="n">
-        <v>2.47184</v>
-      </c>
-      <c r="D38" t="n">
-        <v>655.524</v>
-      </c>
-      <c r="E38" t="n">
-        <v>33.75005792131968</v>
-      </c>
-      <c r="F38" t="n">
-        <v>36.1321</v>
-      </c>
-      <c r="G38" t="n">
-        <v>2.4839</v>
-      </c>
-      <c r="H38" t="n">
-        <v>12</v>
-      </c>
-      <c r="I38" t="n">
-        <v>12</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.1828999999999965</v>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>-3 5 3</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Djurleite</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>000711383</t>
-        </is>
-      </c>
-      <c r="P38" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>6</v>
-      </c>
-      <c r="B39" t="n">
-        <v>36.315</v>
-      </c>
-      <c r="C39" t="n">
-        <v>2.47184</v>
-      </c>
-      <c r="D39" t="n">
-        <v>655.524</v>
-      </c>
-      <c r="E39" t="n">
-        <v>33.75005792131968</v>
-      </c>
-      <c r="F39" t="n">
-        <v>36.1321</v>
-      </c>
-      <c r="G39" t="n">
-        <v>2.4839</v>
-      </c>
-      <c r="H39" t="n">
-        <v>12</v>
-      </c>
-      <c r="I39" t="n">
-        <v>12</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0.1828999999999965</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>3 5 3</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Djurleite</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>000711383</t>
-        </is>
-      </c>
-      <c r="P39" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>7</v>
-      </c>
-      <c r="B40" t="n">
-        <v>37.932</v>
-      </c>
-      <c r="C40" t="n">
-        <v>2.37013</v>
-      </c>
-      <c r="D40" t="n">
-        <v>671.571</v>
-      </c>
-      <c r="E40" t="n">
-        <v>34.5762476252259</v>
-      </c>
-      <c r="F40" t="n">
-        <v>38.0912</v>
-      </c>
-      <c r="G40" t="n">
-        <v>2.3605</v>
-      </c>
-      <c r="H40" t="n">
-        <v>6</v>
-      </c>
-      <c r="I40" t="n">
-        <v>6</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0.1591999999999985</v>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>3 6 2</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>Djurleite</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>000711383</t>
-        </is>
-      </c>
-      <c r="P40" t="n">
+      <c r="R33" t="n">
         <v>1</v>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>7</v>
-      </c>
-      <c r="B41" t="n">
-        <v>37.932</v>
-      </c>
-      <c r="C41" t="n">
-        <v>2.37013</v>
-      </c>
-      <c r="D41" t="n">
-        <v>671.571</v>
-      </c>
-      <c r="E41" t="n">
-        <v>34.5762476252259</v>
-      </c>
-      <c r="F41" t="n">
-        <v>38.0912</v>
-      </c>
-      <c r="G41" t="n">
-        <v>2.3605</v>
-      </c>
-      <c r="H41" t="n">
-        <v>6</v>
-      </c>
-      <c r="I41" t="n">
-        <v>6</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0.1591999999999985</v>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>3 1</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Djurleite</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>000711383</t>
-        </is>
-      </c>
-      <c r="P41" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>7</v>
-      </c>
-      <c r="B42" t="n">
-        <v>37.932</v>
-      </c>
-      <c r="C42" t="n">
-        <v>2.37013</v>
-      </c>
-      <c r="D42" t="n">
-        <v>671.571</v>
-      </c>
-      <c r="E42" t="n">
-        <v>34.5762476252259</v>
-      </c>
-      <c r="F42" t="n">
-        <v>37.7724</v>
-      </c>
-      <c r="G42" t="n">
-        <v>2.3797</v>
-      </c>
-      <c r="H42" t="n">
-        <v>39</v>
-      </c>
-      <c r="I42" t="n">
-        <v>39</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0.1596000000000046</v>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>1 1</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>Djurleite</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>000711383</t>
-        </is>
-      </c>
-      <c r="P42" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>7</v>
-      </c>
-      <c r="B43" t="n">
-        <v>37.932</v>
-      </c>
-      <c r="C43" t="n">
-        <v>2.37013</v>
-      </c>
-      <c r="D43" t="n">
-        <v>671.571</v>
-      </c>
-      <c r="E43" t="n">
-        <v>34.5762476252259</v>
-      </c>
-      <c r="F43" t="n">
-        <v>37.7724</v>
-      </c>
-      <c r="G43" t="n">
-        <v>2.3797</v>
-      </c>
-      <c r="H43" t="n">
-        <v>39</v>
-      </c>
-      <c r="I43" t="n">
-        <v>39</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0.1596000000000046</v>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>11 1 1</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>Djurleite</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>000711383</t>
-        </is>
-      </c>
-      <c r="P43" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>7</v>
-      </c>
-      <c r="B44" t="n">
-        <v>37.932</v>
-      </c>
-      <c r="C44" t="n">
-        <v>2.37013</v>
-      </c>
-      <c r="D44" t="n">
-        <v>671.571</v>
-      </c>
-      <c r="E44" t="n">
-        <v>34.5762476252259</v>
-      </c>
-      <c r="F44" t="n">
-        <v>37.6867</v>
-      </c>
-      <c r="G44" t="n">
-        <v>2.3849</v>
-      </c>
-      <c r="H44" t="n">
-        <v>76</v>
-      </c>
-      <c r="I44" t="n">
-        <v>76</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0.2453000000000003</v>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>8 0 4</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>Djurleite</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>000711383</t>
-        </is>
-      </c>
-      <c r="P44" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>7</v>
-      </c>
-      <c r="B45" t="n">
-        <v>37.932</v>
-      </c>
-      <c r="C45" t="n">
-        <v>2.37013</v>
-      </c>
-      <c r="D45" t="n">
-        <v>671.571</v>
-      </c>
-      <c r="E45" t="n">
-        <v>34.5762476252259</v>
-      </c>
-      <c r="F45" t="n">
-        <v>37.6867</v>
-      </c>
-      <c r="G45" t="n">
-        <v>2.3849</v>
-      </c>
-      <c r="H45" t="n">
-        <v>76</v>
-      </c>
-      <c r="I45" t="n">
-        <v>76</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0.2453000000000003</v>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>2 2</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>Djurleite</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>000711383</t>
-        </is>
-      </c>
-      <c r="P45" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>7</v>
-      </c>
-      <c r="B46" t="n">
-        <v>37.932</v>
-      </c>
-      <c r="C46" t="n">
-        <v>2.37013</v>
-      </c>
-      <c r="D46" t="n">
-        <v>671.571</v>
-      </c>
-      <c r="E46" t="n">
-        <v>34.5762476252259</v>
-      </c>
-      <c r="F46" t="n">
-        <v>37.6687</v>
-      </c>
-      <c r="G46" t="n">
-        <v>2.386</v>
-      </c>
-      <c r="H46" t="n">
-        <v>20</v>
-      </c>
-      <c r="I46" t="n">
-        <v>20</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0.263300000000001</v>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>6 0 12</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Spionkopite</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="P46" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>8</v>
-      </c>
-      <c r="B47" t="n">
-        <v>39.016</v>
-      </c>
-      <c r="C47" t="n">
-        <v>2.30671</v>
-      </c>
-      <c r="D47" t="n">
-        <v>704.095</v>
-      </c>
-      <c r="E47" t="n">
-        <v>36.25076584856021</v>
-      </c>
-      <c r="F47" t="n">
-        <v>39.0597</v>
-      </c>
-      <c r="G47" t="n">
-        <v>2.3042</v>
-      </c>
-      <c r="H47" t="n">
-        <v>126</v>
-      </c>
-      <c r="I47" t="n">
-        <v>12.61261261261261</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0.04370000000000118</v>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>1 0 5</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>Covellite</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>000752233</t>
-        </is>
-      </c>
-      <c r="P47" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>8</v>
-      </c>
-      <c r="B48" t="n">
-        <v>39.016</v>
-      </c>
-      <c r="C48" t="n">
-        <v>2.30671</v>
-      </c>
-      <c r="D48" t="n">
-        <v>704.095</v>
-      </c>
-      <c r="E48" t="n">
-        <v>36.25076584856021</v>
-      </c>
-      <c r="F48" t="n">
-        <v>39.1604</v>
-      </c>
-      <c r="G48" t="n">
-        <v>2.2985</v>
-      </c>
-      <c r="H48" t="n">
-        <v>6</v>
-      </c>
-      <c r="I48" t="n">
-        <v>6</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0.1444000000000045</v>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>-4 6 2</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>Djurleite</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>000711383</t>
-        </is>
-      </c>
-      <c r="P48" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>8</v>
-      </c>
-      <c r="B49" t="n">
-        <v>39.016</v>
-      </c>
-      <c r="C49" t="n">
-        <v>2.30671</v>
-      </c>
-      <c r="D49" t="n">
-        <v>704.095</v>
-      </c>
-      <c r="E49" t="n">
-        <v>36.25076584856021</v>
-      </c>
-      <c r="F49" t="n">
-        <v>39.1604</v>
-      </c>
-      <c r="G49" t="n">
-        <v>2.2985</v>
-      </c>
-      <c r="H49" t="n">
-        <v>6</v>
-      </c>
-      <c r="I49" t="n">
-        <v>6</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0.1444000000000045</v>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>-6 1 5</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>Djurleite</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>000711383</t>
-        </is>
-      </c>
-      <c r="P49" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>8</v>
-      </c>
-      <c r="B50" t="n">
-        <v>39.016</v>
-      </c>
-      <c r="C50" t="n">
-        <v>2.30671</v>
-      </c>
-      <c r="D50" t="n">
-        <v>704.095</v>
-      </c>
-      <c r="E50" t="n">
-        <v>36.25076584856021</v>
-      </c>
-      <c r="F50" t="n">
-        <v>39.1866</v>
-      </c>
-      <c r="G50" t="n">
-        <v>2.297</v>
-      </c>
-      <c r="H50" t="n">
-        <v>25</v>
-      </c>
-      <c r="I50" t="n">
-        <v>25</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0.1706000000000003</v>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>6 0 13</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>Spionkopite</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="P50" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>8</v>
-      </c>
-      <c r="B51" t="n">
-        <v>39.016</v>
-      </c>
-      <c r="C51" t="n">
-        <v>2.30671</v>
-      </c>
-      <c r="D51" t="n">
-        <v>704.095</v>
-      </c>
-      <c r="E51" t="n">
-        <v>36.25076584856021</v>
-      </c>
-      <c r="F51" t="n">
-        <v>38.8318</v>
-      </c>
-      <c r="G51" t="n">
-        <v>2.3172</v>
-      </c>
-      <c r="H51" t="n">
-        <v>6</v>
-      </c>
-      <c r="I51" t="n">
-        <v>6</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0.184199999999997</v>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>-5 2 5</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>Djurleite</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>000711383</t>
-        </is>
-      </c>
-      <c r="P51" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>8</v>
-      </c>
-      <c r="B52" t="n">
-        <v>39.016</v>
-      </c>
-      <c r="C52" t="n">
-        <v>2.30671</v>
-      </c>
-      <c r="D52" t="n">
-        <v>704.095</v>
-      </c>
-      <c r="E52" t="n">
-        <v>36.25076584856021</v>
-      </c>
-      <c r="F52" t="n">
-        <v>38.8318</v>
-      </c>
-      <c r="G52" t="n">
-        <v>2.3172</v>
-      </c>
-      <c r="H52" t="n">
-        <v>6</v>
-      </c>
-      <c r="I52" t="n">
-        <v>6</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0.184199999999997</v>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>5 4 4</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>Djurleite</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>000711383</t>
-        </is>
-      </c>
-      <c r="P52" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>8</v>
-      </c>
-      <c r="B53" t="n">
-        <v>39.016</v>
-      </c>
-      <c r="C53" t="n">
-        <v>2.30671</v>
-      </c>
-      <c r="D53" t="n">
-        <v>704.095</v>
-      </c>
-      <c r="E53" t="n">
-        <v>36.25076584856021</v>
-      </c>
-      <c r="F53" t="n">
-        <v>39.2897</v>
-      </c>
-      <c r="G53" t="n">
-        <v>2.2912</v>
-      </c>
-      <c r="H53" t="n">
-        <v>9</v>
-      </c>
-      <c r="I53" t="n">
-        <v>9</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0.2737000000000052</v>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>7 5 2</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>Djurleite</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>000711383</t>
-        </is>
-      </c>
-      <c r="P53" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>8</v>
-      </c>
-      <c r="B54" t="n">
-        <v>39.016</v>
-      </c>
-      <c r="C54" t="n">
-        <v>2.30671</v>
-      </c>
-      <c r="D54" t="n">
-        <v>704.095</v>
-      </c>
-      <c r="E54" t="n">
-        <v>36.25076584856021</v>
-      </c>
-      <c r="F54" t="n">
-        <v>39.2897</v>
-      </c>
-      <c r="G54" t="n">
-        <v>2.2912</v>
-      </c>
-      <c r="H54" t="n">
-        <v>9</v>
-      </c>
-      <c r="I54" t="n">
-        <v>9</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0.2737000000000052</v>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>-7 5 2</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>Djurleite</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>000711383</t>
-        </is>
-      </c>
-      <c r="P54" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>8</v>
-      </c>
-      <c r="B55" t="n">
-        <v>39.016</v>
-      </c>
-      <c r="C55" t="n">
-        <v>2.30671</v>
-      </c>
-      <c r="D55" t="n">
-        <v>704.095</v>
-      </c>
-      <c r="E55" t="n">
-        <v>36.25076584856021</v>
-      </c>
-      <c r="F55" t="n">
-        <v>38.7261</v>
-      </c>
-      <c r="G55" t="n">
-        <v>2.3233</v>
-      </c>
-      <c r="H55" t="n">
-        <v>8</v>
-      </c>
-      <c r="I55" t="n">
-        <v>8</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0.2898999999999958</v>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>-5 6 1</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>Djurleite</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>000711383</t>
-        </is>
-      </c>
-      <c r="P55" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>8</v>
-      </c>
-      <c r="B56" t="n">
-        <v>39.016</v>
-      </c>
-      <c r="C56" t="n">
-        <v>2.30671</v>
-      </c>
-      <c r="D56" t="n">
-        <v>704.095</v>
-      </c>
-      <c r="E56" t="n">
-        <v>36.25076584856021</v>
-      </c>
-      <c r="F56" t="n">
-        <v>38.7261</v>
-      </c>
-      <c r="G56" t="n">
-        <v>2.3233</v>
-      </c>
-      <c r="H56" t="n">
-        <v>8</v>
-      </c>
-      <c r="I56" t="n">
-        <v>8</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0.2898999999999958</v>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>5 6 1</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>Djurleite</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>000711383</t>
-        </is>
-      </c>
-      <c r="P56" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>11</v>
-      </c>
-      <c r="B57" t="n">
-        <v>41.267</v>
-      </c>
-      <c r="C57" t="n">
-        <v>2.18594</v>
-      </c>
-      <c r="D57" t="n">
-        <v>676.905</v>
-      </c>
-      <c r="E57" t="n">
-        <v>34.85087190893224</v>
-      </c>
-      <c r="F57" t="n">
-        <v>41.2844</v>
-      </c>
-      <c r="G57" t="n">
-        <v>2.185</v>
-      </c>
-      <c r="H57" t="n">
-        <v>8</v>
-      </c>
-      <c r="I57" t="n">
-        <v>8</v>
-      </c>
-      <c r="J57" t="n">
-        <v>0.01739999999999498</v>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>0 0 19</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>Spionkopite</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="P57" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>14</v>
-      </c>
-      <c r="B58" t="n">
-        <v>43.866</v>
-      </c>
-      <c r="C58" t="n">
-        <v>2.06228</v>
-      </c>
-      <c r="D58" t="n">
-        <v>708.8099999999999</v>
-      </c>
-      <c r="E58" t="n">
-        <v>36.49352053503853</v>
-      </c>
-      <c r="F58" t="n">
-        <v>43.9154</v>
-      </c>
-      <c r="G58" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="H58" t="n">
-        <v>8</v>
-      </c>
-      <c r="I58" t="n">
-        <v>8</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0.04939999999999856</v>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>1 0 20</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>Spionkopite</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="P58" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>15</v>
-      </c>
-      <c r="B59" t="n">
-        <v>45.973</v>
-      </c>
-      <c r="C59" t="n">
-        <v>1.97251</v>
-      </c>
-      <c r="D59" t="n">
-        <v>709.143</v>
-      </c>
-      <c r="E59" t="n">
-        <v>36.51066524566362</v>
-      </c>
-      <c r="F59" t="n">
-        <v>46.158</v>
-      </c>
-      <c r="G59" t="n">
-        <v>1.965</v>
-      </c>
-      <c r="H59" t="n">
-        <v>12</v>
-      </c>
-      <c r="I59" t="n">
-        <v>12</v>
-      </c>
-      <c r="J59" t="n">
-        <v>0.1850000000000023</v>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>6 0 17</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>Spionkopite</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="P59" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>17</v>
-      </c>
-      <c r="B60" t="n">
-        <v>48.183</v>
-      </c>
-      <c r="C60" t="n">
-        <v>1.88708</v>
-      </c>
-      <c r="D60" t="n">
-        <v>1942.29</v>
-      </c>
-      <c r="E60" t="n">
-        <v>100</v>
-      </c>
-      <c r="F60" t="n">
-        <v>48.2657</v>
-      </c>
-      <c r="G60" t="n">
-        <v>1.884</v>
-      </c>
-      <c r="H60" t="n">
-        <v>618</v>
-      </c>
-      <c r="I60" t="n">
-        <v>61.86186186186187</v>
-      </c>
-      <c r="J60" t="n">
-        <v>0.08270000000000266</v>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>1 1 0</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>Covellite</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>000752233</t>
-        </is>
-      </c>
-      <c r="P60" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>17</v>
-      </c>
-      <c r="B61" t="n">
-        <v>48.183</v>
-      </c>
-      <c r="C61" t="n">
-        <v>1.88708</v>
-      </c>
-      <c r="D61" t="n">
-        <v>1942.29</v>
-      </c>
-      <c r="E61" t="n">
-        <v>100</v>
-      </c>
-      <c r="F61" t="n">
-        <v>48.0177</v>
-      </c>
-      <c r="G61" t="n">
-        <v>1.8931</v>
-      </c>
-      <c r="H61" t="n">
-        <v>165</v>
-      </c>
-      <c r="I61" t="n">
-        <v>16.51651651651652</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0.165300000000002</v>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>1 0 7</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>Covellite</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>000752233</t>
-        </is>
-      </c>
-      <c r="P61" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>19</v>
-      </c>
-      <c r="B62" t="n">
-        <v>52.849</v>
-      </c>
-      <c r="C62" t="n">
-        <v>1.73095</v>
-      </c>
-      <c r="D62" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E62" t="n">
-        <v>51.4856174927534</v>
-      </c>
-      <c r="F62" t="n">
-        <v>53.0112</v>
-      </c>
-      <c r="G62" t="n">
-        <v>1.726</v>
-      </c>
-      <c r="H62" t="n">
-        <v>256</v>
-      </c>
-      <c r="I62" t="n">
-        <v>25.62562562562562</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0.1622000000000057</v>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>1 0 8</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>Covellite</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>000752233</t>
-        </is>
-      </c>
-      <c r="P62" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>19</v>
-      </c>
-      <c r="B63" t="n">
-        <v>52.849</v>
-      </c>
-      <c r="C63" t="n">
-        <v>1.73095</v>
-      </c>
-      <c r="D63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E63" t="n">
-        <v>51.4856174927534</v>
-      </c>
-      <c r="F63" t="n">
-        <v>52.6163</v>
-      </c>
-      <c r="G63" t="n">
-        <v>1.738</v>
-      </c>
-      <c r="H63" t="n">
-        <v>12</v>
-      </c>
-      <c r="I63" t="n">
-        <v>12</v>
-      </c>
-      <c r="J63" t="n">
-        <v>0.2326999999999941</v>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>6 6 10</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>Spionkopite</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="P63" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>20</v>
-      </c>
-      <c r="B64" t="n">
-        <v>54.629</v>
-      </c>
-      <c r="C64" t="n">
-        <v>1.67867</v>
-      </c>
-      <c r="D64" t="n">
-        <v>752.2859999999999</v>
-      </c>
-      <c r="E64" t="n">
-        <v>38.73190924115348</v>
-      </c>
-      <c r="F64" t="n">
-        <v>54.4403</v>
-      </c>
-      <c r="G64" t="n">
-        <v>1.684</v>
-      </c>
-      <c r="H64" t="n">
-        <v>8</v>
-      </c>
-      <c r="I64" t="n">
-        <v>8</v>
-      </c>
-      <c r="J64" t="n">
-        <v>0.1886999999999972</v>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>4 2 22</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>Spionkopite</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="P64" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>23</v>
-      </c>
-      <c r="B65" t="n">
-        <v>59.335</v>
-      </c>
-      <c r="C65" t="n">
-        <v>1.55626</v>
-      </c>
-      <c r="D65" t="n">
-        <v>1160.67</v>
-      </c>
-      <c r="E65" t="n">
-        <v>59.7578116553141</v>
-      </c>
-      <c r="F65" t="n">
-        <v>59.0765</v>
-      </c>
-      <c r="G65" t="n">
-        <v>1.5624</v>
-      </c>
-      <c r="H65" t="n">
-        <v>104</v>
-      </c>
-      <c r="I65" t="n">
-        <v>10.41041041041041</v>
-      </c>
-      <c r="J65" t="n">
-        <v>0.258499999999998</v>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>2 0 3</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>Covellite</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>000752233</t>
-        </is>
-      </c>
-      <c r="P65" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>26</v>
-      </c>
-      <c r="B66" t="n">
-        <v>63.101</v>
-      </c>
-      <c r="C66" t="n">
-        <v>1.47216</v>
-      </c>
-      <c r="D66" t="n">
-        <v>756.2859999999999</v>
-      </c>
-      <c r="E66" t="n">
-        <v>38.93785171112449</v>
-      </c>
-      <c r="F66" t="n">
-        <v>63.0584</v>
-      </c>
-      <c r="G66" t="n">
-        <v>1.473</v>
-      </c>
-      <c r="H66" t="n">
-        <v>15</v>
-      </c>
-      <c r="I66" t="n">
-        <v>15</v>
-      </c>
-      <c r="J66" t="n">
-        <v>0.04260000000000019</v>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>12 0 13</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>Spionkopite</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="P66" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>27</v>
-      </c>
-      <c r="B67" t="n">
-        <v>65.536</v>
-      </c>
-      <c r="C67" t="n">
-        <v>1.42323</v>
-      </c>
-      <c r="D67" t="n">
-        <v>711.524</v>
-      </c>
-      <c r="E67" t="n">
-        <v>36.63325250091387</v>
-      </c>
-      <c r="F67" t="n">
-        <v>65.5515</v>
-      </c>
-      <c r="G67" t="n">
-        <v>1.4229</v>
-      </c>
-      <c r="H67" t="n">
-        <v>139</v>
-      </c>
-      <c r="I67" t="n">
-        <v>13.91391391391391</v>
-      </c>
-      <c r="J67" t="n">
-        <v>0.01550000000000296</v>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>2 2 2</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>CuCl</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>CuCl</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>000822117</t>
-        </is>
-      </c>
-      <c r="P67" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>27</v>
-      </c>
-      <c r="B68" t="n">
-        <v>65.536</v>
-      </c>
-      <c r="C68" t="n">
-        <v>1.42323</v>
-      </c>
-      <c r="D68" t="n">
-        <v>711.524</v>
-      </c>
-      <c r="E68" t="n">
-        <v>36.63325250091387</v>
-      </c>
-      <c r="F68" t="n">
-        <v>65.4935</v>
-      </c>
-      <c r="G68" t="n">
-        <v>1.424</v>
-      </c>
-      <c r="H68" t="n">
-        <v>8</v>
-      </c>
-      <c r="I68" t="n">
-        <v>8</v>
-      </c>
-      <c r="J68" t="n">
-        <v>0.04250000000000398</v>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>12 0 15</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>Spionkopite</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="P68" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>28</v>
-      </c>
-      <c r="B69" t="n">
-        <v>66.19</v>
-      </c>
-      <c r="C69" t="n">
-        <v>1.41072</v>
-      </c>
-      <c r="D69" t="n">
-        <v>718.857</v>
-      </c>
-      <c r="E69" t="n">
-        <v>37.01079653398823</v>
-      </c>
-      <c r="F69" t="n">
-        <v>66.4396</v>
-      </c>
-      <c r="G69" t="n">
-        <v>1.406</v>
-      </c>
-      <c r="H69" t="n">
-        <v>8</v>
-      </c>
-      <c r="I69" t="n">
-        <v>8</v>
-      </c>
-      <c r="J69" t="n">
-        <v>0.2496000000000009</v>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>6 6 20</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>Spionkopite</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="P69" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>29</v>
-      </c>
-      <c r="B70" t="n">
-        <v>67.541</v>
-      </c>
-      <c r="C70" t="n">
-        <v>1.38576</v>
-      </c>
-      <c r="D70" t="n">
-        <v>735.1900000000001</v>
-      </c>
-      <c r="E70" t="n">
-        <v>37.85171112449737</v>
-      </c>
-      <c r="F70" t="n">
-        <v>67.5258</v>
-      </c>
-      <c r="G70" t="n">
-        <v>1.386</v>
-      </c>
-      <c r="H70" t="n">
-        <v>8</v>
-      </c>
-      <c r="I70" t="n">
-        <v>8</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0.015199999999993</v>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>0 0 30</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>Spionkopite</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="P70" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>31</v>
-      </c>
-      <c r="B71" t="n">
-        <v>68.72799999999999</v>
-      </c>
-      <c r="C71" t="n">
-        <v>1.3647</v>
-      </c>
-      <c r="D71" t="n">
-        <v>708.524</v>
-      </c>
-      <c r="E71" t="n">
-        <v>36.47879564843561</v>
-      </c>
-      <c r="F71" t="n">
-        <v>68.9388</v>
-      </c>
-      <c r="G71" t="n">
-        <v>1.361</v>
-      </c>
-      <c r="H71" t="n">
-        <v>8</v>
-      </c>
-      <c r="I71" t="n">
-        <v>8</v>
-      </c>
-      <c r="J71" t="n">
-        <v>0.2108000000000061</v>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>2 0 7</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>Spionkopite</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="P71" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>35</v>
-      </c>
-      <c r="B72" t="n">
-        <v>74.294</v>
-      </c>
-      <c r="C72" t="n">
-        <v>1.27563</v>
-      </c>
-      <c r="D72" t="n">
-        <v>724.2380000000001</v>
-      </c>
-      <c r="E72" t="n">
-        <v>37.28784064171674</v>
-      </c>
-      <c r="F72" t="n">
-        <v>74.4939</v>
-      </c>
-      <c r="G72" t="n">
-        <v>1.2727</v>
-      </c>
-      <c r="H72" t="n">
-        <v>57</v>
-      </c>
-      <c r="I72" t="n">
-        <v>5.705705705705705</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0.1998999999999995</v>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>2 0 8</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>Covellite</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>000752233</t>
-        </is>
-      </c>
-      <c r="P72" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>36</v>
-      </c>
-      <c r="B73" t="n">
-        <v>74.539</v>
-      </c>
-      <c r="C73" t="n">
-        <v>1.27203</v>
-      </c>
-      <c r="D73" t="n">
-        <v>731.2859999999999</v>
-      </c>
-      <c r="E73" t="n">
-        <v>37.65071127380566</v>
-      </c>
-      <c r="F73" t="n">
-        <v>74.4939</v>
-      </c>
-      <c r="G73" t="n">
-        <v>1.2727</v>
-      </c>
-      <c r="H73" t="n">
-        <v>57</v>
-      </c>
-      <c r="I73" t="n">
-        <v>5.705705705705705</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0.04510000000000502</v>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>2 0 8</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>Covellite</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>000752233</t>
-        </is>
-      </c>
-      <c r="P73" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>38</v>
-      </c>
-      <c r="B74" t="n">
-        <v>76.46299999999999</v>
-      </c>
-      <c r="C74" t="n">
-        <v>1.24475</v>
-      </c>
-      <c r="D74" t="n">
-        <v>684.476</v>
-      </c>
-      <c r="E74" t="n">
-        <v>35.24066951896987</v>
-      </c>
-      <c r="F74" t="n">
-        <v>76.73350000000001</v>
-      </c>
-      <c r="G74" t="n">
-        <v>1.241</v>
-      </c>
-      <c r="H74" t="n">
-        <v>12</v>
-      </c>
-      <c r="I74" t="n">
-        <v>12</v>
-      </c>
-      <c r="J74" t="n">
-        <v>0.2705000000000126</v>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>6 0 31</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>Spionkopite</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="P74" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>39</v>
-      </c>
-      <c r="B75" t="n">
-        <v>76.995</v>
-      </c>
-      <c r="C75" t="n">
-        <v>1.23747</v>
-      </c>
-      <c r="D75" t="n">
-        <v>677.048</v>
-      </c>
-      <c r="E75" t="n">
-        <v>34.8582343522337</v>
-      </c>
-      <c r="F75" t="n">
-        <v>76.73350000000001</v>
-      </c>
-      <c r="G75" t="n">
-        <v>1.241</v>
-      </c>
-      <c r="H75" t="n">
-        <v>12</v>
-      </c>
-      <c r="I75" t="n">
-        <v>12</v>
-      </c>
-      <c r="J75" t="n">
-        <v>0.2614999999999981</v>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>6 0 31</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>Spionkopite</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="P75" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>41</v>
-      </c>
-      <c r="B76" t="n">
-        <v>79.36799999999999</v>
-      </c>
-      <c r="C76" t="n">
-        <v>1.20632</v>
-      </c>
-      <c r="D76" t="n">
-        <v>703.619</v>
-      </c>
-      <c r="E76" t="n">
-        <v>36.22625869463366</v>
-      </c>
-      <c r="F76" t="n">
-        <v>79.6553</v>
-      </c>
-      <c r="G76" t="n">
-        <v>1.2027</v>
-      </c>
-      <c r="H76" t="n">
-        <v>53</v>
-      </c>
-      <c r="I76" t="n">
-        <v>5.305305305305305</v>
-      </c>
-      <c r="J76" t="n">
-        <v>0.2873000000000019</v>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>2 1 3</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>Covellite</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>000752233</t>
-        </is>
-      </c>
-      <c r="P76" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -26354,7 +23048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26443,6 +23137,11 @@
           <t>Status</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Phase_Priority</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -26508,6 +23207,9 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -26573,70 +23275,76 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>30.606</v>
+        <v>32.202</v>
       </c>
       <c r="C4" t="n">
-        <v>2.91866</v>
+        <v>2.77754</v>
       </c>
       <c r="D4" t="n">
-        <v>736.524</v>
+        <v>1366.38</v>
       </c>
       <c r="E4" t="n">
-        <v>37.92039293823271</v>
+        <v>70.3489180297484</v>
       </c>
       <c r="F4" t="n">
-        <v>30.5264</v>
+        <v>31.982</v>
       </c>
       <c r="G4" t="n">
-        <v>2.926</v>
+        <v>2.7961</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07960000000000278</v>
+        <v>0.2199999999999989</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>3 1 12</t>
+          <t>1 0 3</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Cu39S28</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Spionkopite</t>
+          <t>Covellite</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Cu39S28</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>000360380</t>
+          <t>000752233</t>
         </is>
       </c>
       <c r="P4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
         <v>1</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
       </c>
     </row>
     <row r="5">
@@ -26644,55 +23352,55 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>32.202</v>
+        <v>38.996</v>
       </c>
       <c r="C5" t="n">
-        <v>2.77754</v>
+        <v>2.30787</v>
       </c>
       <c r="D5" t="n">
-        <v>1366.38</v>
+        <v>691.2859999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>70.3489180297484</v>
+        <v>35.59128657409553</v>
       </c>
       <c r="F5" t="n">
-        <v>32.2076</v>
+        <v>39.0597</v>
       </c>
       <c r="G5" t="n">
-        <v>2.777</v>
+        <v>2.3042</v>
       </c>
       <c r="H5" t="n">
-        <v>30</v>
+        <v>126</v>
       </c>
       <c r="I5" t="n">
-        <v>30</v>
+        <v>12.61261261261261</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00560000000000116</v>
+        <v>0.0636999999999972</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>6 0 8</t>
+          <t>1 0 5</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Cu39S28</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Spionkopite</t>
+          <t>Covellite</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Cu39S28</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>000360380</t>
+          <t>000752233</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -26702,6 +23410,9 @@
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -26709,55 +23420,55 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>35.394</v>
+        <v>48.183</v>
       </c>
       <c r="C6" t="n">
-        <v>2.53401</v>
+        <v>1.88708</v>
       </c>
       <c r="D6" t="n">
-        <v>655.7619999999999</v>
+        <v>1942.29</v>
       </c>
       <c r="E6" t="n">
-        <v>33.76231149828295</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>35.4426</v>
+        <v>48.2657</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5306</v>
+        <v>1.884</v>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
+        <v>618</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>61.86186186186187</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04860000000000042</v>
+        <v>0.08270000000000266</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-2 6 1</t>
+          <t>1 1 0</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Djurleite</t>
+          <t>Covellite</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000752233</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -26767,6 +23478,9 @@
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -26774,55 +23488,55 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>36.315</v>
+        <v>52.849</v>
       </c>
       <c r="C7" t="n">
-        <v>2.47184</v>
+        <v>1.73095</v>
       </c>
       <c r="D7" t="n">
-        <v>655.524</v>
+        <v>1000</v>
       </c>
       <c r="E7" t="n">
-        <v>33.75005792131968</v>
+        <v>51.4856174927534</v>
       </c>
       <c r="F7" t="n">
-        <v>36.2877</v>
+        <v>53.0112</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4736</v>
+        <v>1.726</v>
       </c>
       <c r="H7" t="n">
-        <v>15</v>
+        <v>256</v>
       </c>
       <c r="I7" t="n">
-        <v>15</v>
+        <v>25.62562562562562</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02729999999999677</v>
+        <v>0.1622000000000057</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>3 6 1</t>
+          <t>1 0 8</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Djurleite</t>
+          <t>Covellite</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000752233</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -26832,6 +23546,9 @@
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -26839,55 +23556,55 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>37.932</v>
+        <v>59.315</v>
       </c>
       <c r="C8" t="n">
-        <v>2.37013</v>
+        <v>1.55675</v>
       </c>
       <c r="D8" t="n">
-        <v>671.571</v>
+        <v>1158.67</v>
       </c>
       <c r="E8" t="n">
-        <v>34.5762476252259</v>
+        <v>59.65484042032858</v>
       </c>
       <c r="F8" t="n">
-        <v>38.0912</v>
+        <v>59.0765</v>
       </c>
       <c r="G8" t="n">
-        <v>2.3605</v>
+        <v>1.5624</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>104</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>10.41041041041041</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1591999999999985</v>
+        <v>0.2384999999999948</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>3 6 2</t>
+          <t>2 0 3</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Djurleite</t>
+          <t>Covellite</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000752233</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -26897,6 +23614,9 @@
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -26904,55 +23624,55 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>39.016</v>
+        <v>63.101</v>
       </c>
       <c r="C9" t="n">
-        <v>2.30671</v>
+        <v>1.47216</v>
       </c>
       <c r="D9" t="n">
-        <v>704.095</v>
+        <v>756.2859999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>36.25076584856021</v>
+        <v>38.93785171112449</v>
       </c>
       <c r="F9" t="n">
-        <v>39.0597</v>
+        <v>63.0584</v>
       </c>
       <c r="G9" t="n">
-        <v>2.3042</v>
+        <v>1.473</v>
       </c>
       <c r="H9" t="n">
-        <v>126</v>
+        <v>15</v>
       </c>
       <c r="I9" t="n">
-        <v>12.61261261261261</v>
+        <v>15</v>
       </c>
       <c r="J9" t="n">
-        <v>0.04370000000000118</v>
+        <v>0.04260000000000019</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1 0 5</t>
+          <t>12 0 13</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu39S28</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Covellite</t>
+          <t>Spionkopite</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu39S28</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>000752233</t>
+          <t>000360380</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -26963,61 +23683,64 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>41.267</v>
+        <v>74.51900000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>2.18594</v>
+        <v>1.27233</v>
       </c>
       <c r="D10" t="n">
-        <v>676.905</v>
+        <v>717.2859999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>34.85087190893224</v>
+        <v>36.92991262890711</v>
       </c>
       <c r="F10" t="n">
-        <v>41.2844</v>
+        <v>74.4939</v>
       </c>
       <c r="G10" t="n">
-        <v>2.185</v>
+        <v>1.2727</v>
       </c>
       <c r="H10" t="n">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>5.705705705705705</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01739999999999498</v>
+        <v>0.025100000000009</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0 0 19</t>
+          <t>2 0 8</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Cu39S28</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Spionkopite</t>
+          <t>Covellite</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Cu39S28</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>000360380</t>
+          <t>000752233</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -27028,1041 +23751,8 @@
           <t>MATCH</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>14</v>
-      </c>
-      <c r="B11" t="n">
-        <v>43.866</v>
-      </c>
-      <c r="C11" t="n">
-        <v>2.06228</v>
-      </c>
-      <c r="D11" t="n">
-        <v>708.8099999999999</v>
-      </c>
-      <c r="E11" t="n">
-        <v>36.49352053503853</v>
-      </c>
-      <c r="F11" t="n">
-        <v>43.9154</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="H11" t="n">
-        <v>8</v>
-      </c>
-      <c r="I11" t="n">
-        <v>8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.04939999999999856</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>1 0 20</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Spionkopite</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
+      <c r="R10" t="n">
         <v>1</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>15</v>
-      </c>
-      <c r="B12" t="n">
-        <v>45.973</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1.97251</v>
-      </c>
-      <c r="D12" t="n">
-        <v>709.143</v>
-      </c>
-      <c r="E12" t="n">
-        <v>36.51066524566362</v>
-      </c>
-      <c r="F12" t="n">
-        <v>46.158</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1.965</v>
-      </c>
-      <c r="H12" t="n">
-        <v>12</v>
-      </c>
-      <c r="I12" t="n">
-        <v>12</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.1850000000000023</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>6 0 17</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Spionkopite</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>17</v>
-      </c>
-      <c r="B13" t="n">
-        <v>48.183</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1.88708</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1942.29</v>
-      </c>
-      <c r="E13" t="n">
-        <v>100</v>
-      </c>
-      <c r="F13" t="n">
-        <v>48.2657</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1.884</v>
-      </c>
-      <c r="H13" t="n">
-        <v>618</v>
-      </c>
-      <c r="I13" t="n">
-        <v>61.86186186186187</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.08270000000000266</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>1 1 0</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Covellite</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>000752233</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>19</v>
-      </c>
-      <c r="B14" t="n">
-        <v>52.849</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1.73095</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E14" t="n">
-        <v>51.4856174927534</v>
-      </c>
-      <c r="F14" t="n">
-        <v>53.0112</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1.726</v>
-      </c>
-      <c r="H14" t="n">
-        <v>256</v>
-      </c>
-      <c r="I14" t="n">
-        <v>25.62562562562562</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.1622000000000057</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>1 0 8</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Covellite</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>000752233</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>20</v>
-      </c>
-      <c r="B15" t="n">
-        <v>54.629</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1.67867</v>
-      </c>
-      <c r="D15" t="n">
-        <v>752.2859999999999</v>
-      </c>
-      <c r="E15" t="n">
-        <v>38.73190924115348</v>
-      </c>
-      <c r="F15" t="n">
-        <v>54.4403</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1.684</v>
-      </c>
-      <c r="H15" t="n">
-        <v>8</v>
-      </c>
-      <c r="I15" t="n">
-        <v>8</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.1886999999999972</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>4 2 22</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Spionkopite</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>23</v>
-      </c>
-      <c r="B16" t="n">
-        <v>59.335</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1.55626</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1160.67</v>
-      </c>
-      <c r="E16" t="n">
-        <v>59.7578116553141</v>
-      </c>
-      <c r="F16" t="n">
-        <v>59.0765</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1.5624</v>
-      </c>
-      <c r="H16" t="n">
-        <v>104</v>
-      </c>
-      <c r="I16" t="n">
-        <v>10.41041041041041</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.258499999999998</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2 0 3</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Covellite</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>000752233</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>26</v>
-      </c>
-      <c r="B17" t="n">
-        <v>63.101</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1.47216</v>
-      </c>
-      <c r="D17" t="n">
-        <v>756.2859999999999</v>
-      </c>
-      <c r="E17" t="n">
-        <v>38.93785171112449</v>
-      </c>
-      <c r="F17" t="n">
-        <v>63.0584</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1.473</v>
-      </c>
-      <c r="H17" t="n">
-        <v>15</v>
-      </c>
-      <c r="I17" t="n">
-        <v>15</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.04260000000000019</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>12 0 13</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Spionkopite</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>27</v>
-      </c>
-      <c r="B18" t="n">
-        <v>65.536</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1.42323</v>
-      </c>
-      <c r="D18" t="n">
-        <v>711.524</v>
-      </c>
-      <c r="E18" t="n">
-        <v>36.63325250091387</v>
-      </c>
-      <c r="F18" t="n">
-        <v>65.5515</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1.4229</v>
-      </c>
-      <c r="H18" t="n">
-        <v>139</v>
-      </c>
-      <c r="I18" t="n">
-        <v>13.91391391391391</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.01550000000000296</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2 2 2</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>CuCl</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>CuCl</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>000822117</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>28</v>
-      </c>
-      <c r="B19" t="n">
-        <v>66.19</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1.41072</v>
-      </c>
-      <c r="D19" t="n">
-        <v>718.857</v>
-      </c>
-      <c r="E19" t="n">
-        <v>37.01079653398823</v>
-      </c>
-      <c r="F19" t="n">
-        <v>66.4396</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1.406</v>
-      </c>
-      <c r="H19" t="n">
-        <v>8</v>
-      </c>
-      <c r="I19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.2496000000000009</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>6 6 20</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Spionkopite</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>29</v>
-      </c>
-      <c r="B20" t="n">
-        <v>67.541</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1.38576</v>
-      </c>
-      <c r="D20" t="n">
-        <v>735.1900000000001</v>
-      </c>
-      <c r="E20" t="n">
-        <v>37.85171112449737</v>
-      </c>
-      <c r="F20" t="n">
-        <v>67.5258</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1.386</v>
-      </c>
-      <c r="H20" t="n">
-        <v>8</v>
-      </c>
-      <c r="I20" t="n">
-        <v>8</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.015199999999993</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>0 0 30</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Spionkopite</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>31</v>
-      </c>
-      <c r="B21" t="n">
-        <v>68.72799999999999</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1.3647</v>
-      </c>
-      <c r="D21" t="n">
-        <v>708.524</v>
-      </c>
-      <c r="E21" t="n">
-        <v>36.47879564843561</v>
-      </c>
-      <c r="F21" t="n">
-        <v>68.9388</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1.361</v>
-      </c>
-      <c r="H21" t="n">
-        <v>8</v>
-      </c>
-      <c r="I21" t="n">
-        <v>8</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.2108000000000061</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2 0 7</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Spionkopite</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>35</v>
-      </c>
-      <c r="B22" t="n">
-        <v>74.294</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1.27563</v>
-      </c>
-      <c r="D22" t="n">
-        <v>724.2380000000001</v>
-      </c>
-      <c r="E22" t="n">
-        <v>37.28784064171674</v>
-      </c>
-      <c r="F22" t="n">
-        <v>74.4939</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1.2727</v>
-      </c>
-      <c r="H22" t="n">
-        <v>57</v>
-      </c>
-      <c r="I22" t="n">
-        <v>5.705705705705705</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.1998999999999995</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2 0 8</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Covellite</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>000752233</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>36</v>
-      </c>
-      <c r="B23" t="n">
-        <v>74.539</v>
-      </c>
-      <c r="C23" t="n">
-        <v>1.27203</v>
-      </c>
-      <c r="D23" t="n">
-        <v>731.2859999999999</v>
-      </c>
-      <c r="E23" t="n">
-        <v>37.65071127380566</v>
-      </c>
-      <c r="F23" t="n">
-        <v>74.4939</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1.2727</v>
-      </c>
-      <c r="H23" t="n">
-        <v>57</v>
-      </c>
-      <c r="I23" t="n">
-        <v>5.705705705705705</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.04510000000000502</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2 0 8</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Covellite</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>000752233</t>
-        </is>
-      </c>
-      <c r="P23" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>38</v>
-      </c>
-      <c r="B24" t="n">
-        <v>76.46299999999999</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1.24475</v>
-      </c>
-      <c r="D24" t="n">
-        <v>684.476</v>
-      </c>
-      <c r="E24" t="n">
-        <v>35.24066951896987</v>
-      </c>
-      <c r="F24" t="n">
-        <v>76.73350000000001</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1.241</v>
-      </c>
-      <c r="H24" t="n">
-        <v>12</v>
-      </c>
-      <c r="I24" t="n">
-        <v>12</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.2705000000000126</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>6 0 31</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Spionkopite</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="P24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>39</v>
-      </c>
-      <c r="B25" t="n">
-        <v>76.995</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1.23747</v>
-      </c>
-      <c r="D25" t="n">
-        <v>677.048</v>
-      </c>
-      <c r="E25" t="n">
-        <v>34.8582343522337</v>
-      </c>
-      <c r="F25" t="n">
-        <v>76.73350000000001</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1.241</v>
-      </c>
-      <c r="H25" t="n">
-        <v>12</v>
-      </c>
-      <c r="I25" t="n">
-        <v>12</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.2614999999999981</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>6 0 31</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Spionkopite</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="P25" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>41</v>
-      </c>
-      <c r="B26" t="n">
-        <v>79.36799999999999</v>
-      </c>
-      <c r="C26" t="n">
-        <v>1.20632</v>
-      </c>
-      <c r="D26" t="n">
-        <v>703.619</v>
-      </c>
-      <c r="E26" t="n">
-        <v>36.22625869463366</v>
-      </c>
-      <c r="F26" t="n">
-        <v>79.6553</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1.2027</v>
-      </c>
-      <c r="H26" t="n">
-        <v>53</v>
-      </c>
-      <c r="I26" t="n">
-        <v>5.305305305305305</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.2873000000000019</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>2 1 3</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Covellite</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>000752233</t>
-        </is>
-      </c>
-      <c r="P26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -28076,7 +23766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28136,604 +23826,34 @@
         <v>9</v>
       </c>
       <c r="B2" t="n">
-        <v>40.121</v>
+        <v>70.14</v>
       </c>
       <c r="C2" t="n">
-        <v>2.24569</v>
+        <v>1.34065</v>
       </c>
       <c r="D2" t="n">
-        <v>663.2859999999999</v>
+        <v>732.571</v>
       </c>
       <c r="E2" t="n">
-        <v>34.14968928429843</v>
+        <v>37.71687029228386</v>
       </c>
       <c r="F2" t="n">
-        <v>39.2897</v>
+        <v>69.749</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000752233</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.8312999999999988</v>
+        <v>0.3910000000000053</v>
       </c>
       <c r="J2" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>10</v>
-      </c>
-      <c r="B3" t="n">
-        <v>40.735</v>
-      </c>
-      <c r="C3" t="n">
-        <v>2.21325</v>
-      </c>
-      <c r="D3" t="n">
-        <v>664.524</v>
-      </c>
-      <c r="E3" t="n">
-        <v>34.21342847875446</v>
-      </c>
-      <c r="F3" t="n">
-        <v>41.2844</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>0.5493999999999986</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B4" t="n">
-        <v>41.881</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2.15531</v>
-      </c>
-      <c r="D4" t="n">
-        <v>675.333</v>
-      </c>
-      <c r="E4" t="n">
-        <v>34.76993651823363</v>
-      </c>
-      <c r="F4" t="n">
-        <v>41.2844</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>0.5966000000000022</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B5" t="n">
-        <v>43.006</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2.10148</v>
-      </c>
-      <c r="D5" t="n">
-        <v>711.476</v>
-      </c>
-      <c r="E5" t="n">
-        <v>36.63078119127422</v>
-      </c>
-      <c r="F5" t="n">
-        <v>42.5477</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>0.4583000000000013</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>16</v>
-      </c>
-      <c r="B6" t="n">
-        <v>46.853</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1.9375</v>
-      </c>
-      <c r="D6" t="n">
-        <v>770.7619999999999</v>
-      </c>
-      <c r="E6" t="n">
-        <v>39.6831575099496</v>
-      </c>
-      <c r="F6" t="n">
-        <v>46.158</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>0.6950000000000003</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B7" t="n">
-        <v>50.598</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1.80254</v>
-      </c>
-      <c r="D7" t="n">
-        <v>773.095</v>
-      </c>
-      <c r="E7" t="n">
-        <v>39.80327345556019</v>
-      </c>
-      <c r="F7" t="n">
-        <v>50.0775</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>0.5204999999999984</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>21</v>
-      </c>
-      <c r="B8" t="n">
-        <v>55.877</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1.6441</v>
-      </c>
-      <c r="D8" t="n">
-        <v>749.095</v>
-      </c>
-      <c r="E8" t="n">
-        <v>38.56761863573411</v>
-      </c>
-      <c r="F8" t="n">
-        <v>56.7051</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>0.8280999999999992</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>22</v>
-      </c>
-      <c r="B9" t="n">
-        <v>57.351</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.60531</v>
-      </c>
-      <c r="D9" t="n">
-        <v>827.2859999999999</v>
-      </c>
-      <c r="E9" t="n">
-        <v>42.59333055310999</v>
-      </c>
-      <c r="F9" t="n">
-        <v>56.7051</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>0.6458999999999975</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>24</v>
-      </c>
-      <c r="B10" t="n">
-        <v>61.648</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1.50332</v>
-      </c>
-      <c r="D10" t="n">
-        <v>760.2380000000001</v>
-      </c>
-      <c r="E10" t="n">
-        <v>39.14132287145586</v>
-      </c>
-      <c r="F10" t="n">
-        <v>63.0584</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.410399999999996</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>25</v>
-      </c>
-      <c r="B11" t="n">
-        <v>62.302</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1.48908</v>
-      </c>
-      <c r="D11" t="n">
-        <v>740.667</v>
-      </c>
-      <c r="E11" t="n">
-        <v>38.13369785150518</v>
-      </c>
-      <c r="F11" t="n">
-        <v>63.0584</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.7563999999999993</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>30</v>
-      </c>
-      <c r="B12" t="n">
-        <v>67.95</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1.37841</v>
-      </c>
-      <c r="D12" t="n">
-        <v>721.905</v>
-      </c>
-      <c r="E12" t="n">
-        <v>37.16772469610614</v>
-      </c>
-      <c r="F12" t="n">
-        <v>67.5258</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>0.424199999999999</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>32</v>
-      </c>
-      <c r="B13" t="n">
-        <v>70.16</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1.3403</v>
-      </c>
-      <c r="D13" t="n">
-        <v>743.2859999999999</v>
-      </c>
-      <c r="E13" t="n">
-        <v>38.2685386837187</v>
-      </c>
-      <c r="F13" t="n">
-        <v>69.749</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>000752233</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.4110000000000014</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>33</v>
-      </c>
-      <c r="B14" t="n">
-        <v>71.797</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1.31372</v>
-      </c>
-      <c r="D14" t="n">
-        <v>693.571</v>
-      </c>
-      <c r="E14" t="n">
-        <v>35.70893121006647</v>
-      </c>
-      <c r="F14" t="n">
-        <v>71.3383</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>0.4586999999999932</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>34</v>
-      </c>
-      <c r="B15" t="n">
-        <v>73.782</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1.2832</v>
-      </c>
-      <c r="D15" t="n">
-        <v>729.333</v>
-      </c>
-      <c r="E15" t="n">
-        <v>37.55015986284231</v>
-      </c>
-      <c r="F15" t="n">
-        <v>74.4939</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>000752233</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>0.7119</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>37</v>
-      </c>
-      <c r="B16" t="n">
-        <v>75.971</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1.25157</v>
-      </c>
-      <c r="D16" t="n">
-        <v>668.667</v>
-      </c>
-      <c r="E16" t="n">
-        <v>34.42673339202694</v>
-      </c>
-      <c r="F16" t="n">
-        <v>76.73350000000001</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>0.7625000000000028</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>40</v>
-      </c>
-      <c r="B17" t="n">
-        <v>78.161</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1.2219</v>
-      </c>
-      <c r="D17" t="n">
-        <v>704.476</v>
-      </c>
-      <c r="E17" t="n">
-        <v>36.27038186882495</v>
-      </c>
-      <c r="F17" t="n">
-        <v>77.37909999999999</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>CuCl</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>000822117</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>0.7819000000000074</v>
-      </c>
-      <c r="J17" t="inlineStr">
         <is>
           <t>NO MATCH</t>
         </is>
@@ -28750,7 +23870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28813,169 +23933,130 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>000360380</t>
+          <t>000752233</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cu39S28</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Spionkopite</t>
+          <t>Covellite</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cu39S28</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1444000000000001</v>
+        <v>0.1233250000000008</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2705000000000126</v>
+        <v>0.2384999999999948</v>
       </c>
       <c r="H2" t="n">
-        <v>667.9302781767913</v>
+        <v>459.3378949590432</v>
       </c>
       <c r="I2" t="n">
-        <v>41.46341463414634</v>
+        <v>80</v>
       </c>
       <c r="J2" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="K2" t="n">
-        <v>54.83870967741935</v>
+        <v>53.33333333333334</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>000752233</t>
+          <t>000711383</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Covellite</t>
+          <t>Djurleite</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1493800000000011</v>
+        <v>0.1536749999999989</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2873000000000019</v>
+        <v>0.2071999999999967</v>
       </c>
       <c r="H3" t="n">
-        <v>534.3352434497424</v>
+        <v>211.2675244170541</v>
       </c>
       <c r="I3" t="n">
-        <v>24.39024390243902</v>
+        <v>40</v>
       </c>
       <c r="J3" t="n">
-        <v>15</v>
+        <v>116</v>
       </c>
       <c r="K3" t="n">
-        <v>66.66666666666666</v>
+        <v>3.448275862068965</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000360380</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>Cu39S28</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Djurleite</t>
+          <t>Spionkopite</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>Cu39S28</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1251499999999992</v>
+        <v>0.117874999999998</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2071999999999967</v>
+        <v>0.2326999999999941</v>
       </c>
       <c r="H4" t="n">
-        <v>351.93601367458</v>
+        <v>196.3636738077218</v>
       </c>
       <c r="I4" t="n">
-        <v>19.51219512195122</v>
+        <v>40</v>
       </c>
       <c r="J4" t="n">
-        <v>116</v>
+        <v>31</v>
       </c>
       <c r="K4" t="n">
-        <v>6.896551724137931</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>000822117</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>CuCl</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CuCl</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.06325000000000358</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.1110000000000042</v>
-      </c>
-      <c r="H5" t="n">
-        <v>70.38331042223355</v>
-      </c>
-      <c r="I5" t="n">
-        <v>4.878048780487805</v>
-      </c>
-      <c r="J5" t="n">
-        <v>5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>40</v>
+        <v>12.90322580645161</v>
       </c>
     </row>
   </sheetData>
